--- a/2025 업무일지.xlsx
+++ b/2025 업무일지.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28602"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C83FCF4-A814-4724-832B-43C1BF9BF37E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E81E387-577C-4854-ADD5-6D7110439A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="11895" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="320">
   <si>
     <t>테마</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -727,17 +727,33 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">/중공사 3천원 적립일정
+      <t>/이러닝 듣기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+/중공사 3천원 적립일정
 </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FFD9D9D9"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">/아비쥬 겨제 예약
@@ -747,27 +763,22 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">/올리브영 스킨, 선크림구매
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">/아쿠아디파르마
+/아쿠아디파르마
 </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FFD9D9D9"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t>/무코타, 金</t>
@@ -776,7 +787,9 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">七彩
@@ -786,11 +799,25 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FFF2F2F2"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
       <t>/코스트코 닥터지 선크림, 로션 가격</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFF2F2F2"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>레슨 7회차 2시+아스크림</t>
@@ -800,7 +827,7 @@
     <t>자유연습</t>
   </si>
   <si>
-    <t>레슨 8회차</t>
+    <t>레슨 8회차 8:30</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -812,6 +839,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>BMW문의</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>라경찬 2시</t>
   </si>
   <si>
@@ -826,6 +857,13 @@
     <t>이러닝 시작</t>
   </si>
   <si>
+    <t>아쿠아디파르마</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6:30 커피챗</t>
+  </si>
+  <si>
     <t>팬티형생리대 왕창주문</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -838,14 +876,29 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>아빠 말해주기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI 캠프 미션수행</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>올영 연작 테스트</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>정보처리기사 이론공부</t>
+  </si>
+  <si>
     <t>조아 릴리이드예약</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>제이드 취소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>겨제 1회차 1:30</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -857,7 +910,7 @@
     <t>PPT완성</t>
   </si>
   <si>
-    <t>정보처리기사 이론공부</t>
+    <t>https://www.seocho.go.kr/site/seocho/04/10409030206002019112603.jsp</t>
   </si>
   <si>
     <t>무코타 홈케어</t>
@@ -867,11 +920,20 @@
     <t>8토</t>
   </si>
   <si>
+    <t>10월</t>
+  </si>
+  <si>
     <t>미간보톡스</t>
   </si>
   <si>
-    <t>제이드12시</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>베일러 12:30</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카오위 6:30</t>
+  </si>
+  <si>
+    <t>여동기</t>
   </si>
   <si>
     <t>프로님 코엑스방문</t>
@@ -1186,6 +1248,34 @@
   </si>
   <si>
     <t>원래 33,000원인데 적립금 털어서 이 가격</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴아티 히알루론산</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5cc (주사2개)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강남역 베러미의원</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>깊게맞으면 엠보없지만 멍이 좀 들수있다/ 얕게맞으면 엠보있고 좀 아프지만 멍은 없다 2가지 옵션을 제시해줘서 좋았음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈바로밑에도 놔주면 좋았을텐데 그렇진않았다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>올리지오</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신사 베일러의원</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1414,12 +1504,17 @@
     <t>https://dashboard.ngrok.com/get-started/setup/windows</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>Android Studio</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
@@ -1557,25 +1652,34 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFD9D9D9"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFF2F2F2"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1746,7 +1850,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1756,8 +1860,14 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1896,10 +2006,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1950,12 +2069,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
+    <cellStyle name="Hyperlink" xfId="4" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="쉼표 [0]" xfId="3" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
@@ -2271,34 +2389,34 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62">
+      <c r="C1" s="65">
         <v>1</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="62">
+      <c r="D1" s="66"/>
+      <c r="E1" s="65">
         <v>2</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="62">
+      <c r="F1" s="66"/>
+      <c r="G1" s="65">
         <v>3</v>
       </c>
-      <c r="H1" s="63"/>
-      <c r="I1" s="62" t="s">
+      <c r="H1" s="66"/>
+      <c r="I1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="63"/>
-      <c r="K1" s="62">
+      <c r="J1" s="66"/>
+      <c r="K1" s="65">
         <v>5</v>
       </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="62">
+      <c r="L1" s="66"/>
+      <c r="M1" s="65">
         <v>6</v>
       </c>
-      <c r="N1" s="63"/>
-      <c r="O1" s="62" t="s">
+      <c r="N1" s="66"/>
+      <c r="O1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="63"/>
+      <c r="P1" s="66"/>
       <c r="Q1" s="2" t="s">
         <v>4</v>
       </c>
@@ -2312,9 +2430,9 @@
       <c r="U1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
       <c r="Y1" s="7"/>
       <c r="Z1" s="7"/>
     </row>
@@ -2325,32 +2443,32 @@
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="56">
+      <c r="C2" s="59">
         <v>0.30555555555555552</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
       <c r="V2" s="10"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
     </row>
@@ -2379,16 +2497,16 @@
       <c r="N3" s="13"/>
       <c r="O3" s="14"/>
       <c r="P3" s="13"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47" t="s">
+      <c r="Q3" s="54"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
     </row>
@@ -2405,15 +2523,15 @@
       <c r="F4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="47"/>
+      <c r="G4" s="49"/>
       <c r="H4" s="13"/>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="49" t="s">
         <v>18</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="49" t="s">
         <v>19</v>
       </c>
       <c r="L4" s="13" t="s">
@@ -2425,22 +2543,22 @@
       <c r="N4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="47" t="s">
+      <c r="O4" s="49" t="s">
         <v>19</v>
       </c>
       <c r="P4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47" t="s">
+      <c r="Q4" s="54"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="47"/>
+      <c r="T4" s="49"/>
       <c r="U4" s="15"/>
       <c r="V4" s="7"/>
       <c r="W4" s="7"/>
-      <c r="X4" s="47"/>
+      <c r="X4" s="49"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
     </row>
@@ -2463,46 +2581,46 @@
       <c r="N5" s="13"/>
       <c r="O5" s="12"/>
       <c r="P5" s="13"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47" t="s">
+      <c r="Q5" s="54"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="T5" s="47"/>
+      <c r="T5" s="49"/>
       <c r="U5" s="15"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
-      <c r="X5" s="47"/>
+      <c r="X5" s="49"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
     </row>
     <row r="6" spans="1:26" ht="17.25">
       <c r="A6" s="8"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47" t="s">
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="49"/>
       <c r="U6" s="15"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
     </row>
     <row r="7" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A7" s="8" t="s">
@@ -2543,18 +2661,18 @@
       <c r="P7" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47" t="s">
+      <c r="Q7" s="54"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="T7" s="47"/>
+      <c r="T7" s="49"/>
       <c r="U7" s="15"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
     </row>
     <row r="8" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A8" s="8"/>
@@ -2587,18 +2705,18 @@
       <c r="P8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47" t="s">
+      <c r="Q8" s="54"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="T8" s="47"/>
+      <c r="T8" s="49"/>
       <c r="U8" s="15"/>
-      <c r="V8" s="47"/>
+      <c r="V8" s="49"/>
       <c r="W8" s="7"/>
-      <c r="X8" s="47"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
+      <c r="Z8" s="49"/>
     </row>
     <row r="9" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A9" s="8"/>
@@ -2627,19 +2745,19 @@
       <c r="N9" s="13"/>
       <c r="O9" s="12"/>
       <c r="P9" s="13"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
       <c r="U9" s="15"/>
       <c r="V9" s="17"/>
       <c r="W9" s="18"/>
       <c r="X9" s="17"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
     </row>
     <row r="10" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A10" s="47"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
       <c r="D10" s="13"/>
@@ -2659,16 +2777,16 @@
       <c r="N10" s="13"/>
       <c r="O10" s="12"/>
       <c r="P10" s="13"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
       <c r="U10" s="15"/>
-      <c r="V10" s="47"/>
+      <c r="V10" s="49"/>
       <c r="W10" s="7"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
     </row>
     <row r="11" spans="1:26" s="6" customFormat="1" ht="17.25">
       <c r="A11" s="8"/>
@@ -2689,18 +2807,18 @@
       <c r="L11" s="13"/>
       <c r="M11" s="12"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="47"/>
+      <c r="O11" s="49"/>
       <c r="P11" s="13"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
       <c r="U11" s="15"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="47"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
     </row>
     <row r="12" spans="1:26" s="6" customFormat="1" ht="17.25">
       <c r="A12" s="8"/>
@@ -2723,16 +2841,16 @@
       <c r="N12" s="13"/>
       <c r="O12" s="12"/>
       <c r="P12" s="13"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
       <c r="W12" s="17"/>
       <c r="X12" s="17"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
     </row>
     <row r="13" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A13" s="8"/>
@@ -2755,21 +2873,21 @@
       <c r="N13" s="13"/>
       <c r="O13" s="12"/>
       <c r="P13" s="13"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="46" t="s">
+      <c r="Q13" s="54"/>
+      <c r="R13" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
     </row>
     <row r="14" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A14" s="47"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="11"/>
       <c r="C14" s="19"/>
       <c r="D14" s="13"/>
@@ -2785,16 +2903,16 @@
       <c r="N14" s="13"/>
       <c r="O14" s="19"/>
       <c r="P14" s="13"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
     </row>
     <row r="15" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A15" s="8"/>
@@ -2813,16 +2931,16 @@
       <c r="N15" s="13"/>
       <c r="O15" s="12"/>
       <c r="P15" s="13"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="47"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
     </row>
     <row r="16" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A16" s="8"/>
@@ -2841,43 +2959,43 @@
       <c r="N16" s="13"/>
       <c r="O16" s="12"/>
       <c r="P16" s="13"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="47"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="47"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
     </row>
     <row r="17" spans="1:20" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="47"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
     </row>
     <row r="18" spans="1:20" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A18" s="47"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="11" t="s">
         <v>46</v>
       </c>
@@ -2895,13 +3013,13 @@
       <c r="N18" s="13"/>
       <c r="O18" s="12"/>
       <c r="P18" s="13"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="47"/>
-      <c r="T18" s="47"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="49"/>
     </row>
     <row r="19" spans="1:20" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A19" s="47"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="11" t="s">
         <v>47</v>
       </c>
@@ -2939,52 +3057,52 @@
       </c>
       <c r="O19" s="12"/>
       <c r="P19" s="13"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
     </row>
     <row r="20" spans="1:20" s="6" customFormat="1" ht="17.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="47"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
       <c r="T20" s="10"/>
     </row>
     <row r="21" spans="1:20" ht="30.75" customHeight="1">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
       <c r="T21" s="10"/>
     </row>
     <row r="22" spans="1:20" s="6" customFormat="1" ht="30.75" customHeight="1">
@@ -2994,38 +3112,38 @@
       <c r="B22" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="61" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="58">
+      <c r="D22" s="62"/>
+      <c r="E22" s="61">
         <v>9</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="58">
+      <c r="F22" s="62"/>
+      <c r="G22" s="61">
         <v>10</v>
       </c>
-      <c r="H22" s="59"/>
-      <c r="I22" s="58" t="s">
+      <c r="H22" s="62"/>
+      <c r="I22" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="J22" s="59"/>
-      <c r="K22" s="58" t="s">
+      <c r="J22" s="62"/>
+      <c r="K22" s="61" t="s">
         <v>53</v>
       </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="58" t="s">
+      <c r="L22" s="62"/>
+      <c r="M22" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="N22" s="59"/>
-      <c r="O22" s="58">
-        <v>14</v>
-      </c>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="47"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="61">
+        <v>14</v>
+      </c>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="49"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="49"/>
     </row>
     <row r="23" spans="1:20" s="6" customFormat="1" ht="20.25">
       <c r="A23" s="22" t="s">
@@ -3034,26 +3152,26 @@
       <c r="B23" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="56"/>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="48" t="s">
+      <c r="C23" s="59"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
     </row>
     <row r="24" spans="1:20" s="6" customFormat="1" ht="17.25">
       <c r="A24" s="8" t="s">
@@ -3080,17 +3198,17 @@
       <c r="N24" s="13"/>
       <c r="O24" s="14"/>
       <c r="P24" s="13"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="47"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="49"/>
       <c r="S24" s="23"/>
-      <c r="T24" s="47"/>
+      <c r="T24" s="49"/>
     </row>
     <row r="25" spans="1:20" s="6" customFormat="1" ht="28.5" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="49" t="s">
         <v>56</v>
       </c>
       <c r="D25" s="13" t="s">
@@ -3098,7 +3216,7 @@
       </c>
       <c r="E25" s="14"/>
       <c r="F25" s="13"/>
-      <c r="G25" s="47"/>
+      <c r="G25" s="49"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14" t="s">
         <v>17</v>
@@ -3108,7 +3226,7 @@
       </c>
       <c r="K25" s="14"/>
       <c r="L25" s="13"/>
-      <c r="M25" s="47" t="s">
+      <c r="M25" s="49" t="s">
         <v>57</v>
       </c>
       <c r="N25" s="13" t="s">
@@ -3116,8 +3234,8 @@
       </c>
       <c r="O25" s="14"/>
       <c r="P25" s="13"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="47"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="49"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
     </row>
@@ -3140,7 +3258,7 @@
       <c r="N26" s="13"/>
       <c r="O26" s="12"/>
       <c r="P26" s="13"/>
-      <c r="Q26" s="49"/>
+      <c r="Q26" s="52"/>
       <c r="R26" s="27"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -3148,21 +3266,21 @@
     <row r="27" spans="1:20" s="6" customFormat="1" ht="17.25">
       <c r="A27" s="8"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="49"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="52"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="28"/>
@@ -3200,10 +3318,10 @@
         <v>61</v>
       </c>
       <c r="P28" s="13"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="47"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="49"/>
       <c r="S28" s="29"/>
-      <c r="T28" s="47"/>
+      <c r="T28" s="49"/>
     </row>
     <row r="29" spans="1:20" s="6" customFormat="1" ht="34.15" customHeight="1">
       <c r="A29" s="8"/>
@@ -3238,7 +3356,7 @@
       <c r="P29" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q29" s="49"/>
+      <c r="Q29" s="52"/>
       <c r="R29" s="28"/>
       <c r="S29" s="23"/>
       <c r="T29" s="28"/>
@@ -3270,13 +3388,13 @@
         <v>68</v>
       </c>
       <c r="P30" s="13"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="47"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="49"/>
       <c r="S30" s="25"/>
       <c r="T30" s="28"/>
     </row>
     <row r="31" spans="1:20" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A31" s="47"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12"/>
       <c r="D31" s="13"/>
@@ -3300,7 +3418,7 @@
       </c>
       <c r="O31" s="12"/>
       <c r="P31" s="13"/>
-      <c r="Q31" s="49"/>
+      <c r="Q31" s="52"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="28"/>
@@ -3328,7 +3446,7 @@
       </c>
       <c r="O32" s="12"/>
       <c r="P32" s="13"/>
-      <c r="Q32" s="49"/>
+      <c r="Q32" s="52"/>
       <c r="R32" s="30"/>
       <c r="S32" s="30"/>
       <c r="T32" s="30"/>
@@ -3358,16 +3476,16 @@
       </c>
       <c r="O33" s="12"/>
       <c r="P33" s="13"/>
-      <c r="Q33" s="49"/>
+      <c r="Q33" s="52"/>
       <c r="R33" s="30"/>
       <c r="S33" s="30"/>
       <c r="T33" s="30"/>
-      <c r="U33" s="47"/>
-      <c r="V33" s="47"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="47"/>
-      <c r="Y33" s="47"/>
-      <c r="Z33" s="47"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="49"/>
+      <c r="W33" s="49"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="49"/>
     </row>
     <row r="34" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A34" s="8"/>
@@ -3390,19 +3508,19 @@
       </c>
       <c r="O34" s="12"/>
       <c r="P34" s="13"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
+      <c r="Q34" s="52"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
     </row>
     <row r="35" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A35" s="47"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="11"/>
       <c r="C35" s="19"/>
       <c r="D35" s="13"/>
@@ -3422,16 +3540,16 @@
       <c r="N35" s="13"/>
       <c r="O35" s="19"/>
       <c r="P35" s="13"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="47"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="49"/>
       <c r="S35" s="31"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="49"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
+      <c r="Z35" s="49"/>
     </row>
     <row r="36" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
       <c r="A36" s="8"/>
@@ -3450,12 +3568,12 @@
       <c r="N36" s="13"/>
       <c r="O36" s="12"/>
       <c r="P36" s="13"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="47"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="49"/>
       <c r="S36" s="31"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="47"/>
-      <c r="V36" s="47"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
@@ -3478,12 +3596,12 @@
       <c r="N37" s="13"/>
       <c r="O37" s="12"/>
       <c r="P37" s="13"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="47"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="49"/>
       <c r="S37" s="31"/>
-      <c r="T37" s="47"/>
-      <c r="U37" s="47"/>
-      <c r="V37" s="47"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -3494,33 +3612,33 @@
       <c r="B38" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="54"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="54"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="47"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="49"/>
       <c r="S38" s="31"/>
-      <c r="T38" s="47"/>
-      <c r="U38" s="47"/>
-      <c r="V38" s="47"/>
+      <c r="T38" s="49"/>
+      <c r="U38" s="49"/>
+      <c r="V38" s="49"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
     </row>
     <row r="39" spans="1:26" s="6" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A39" s="47"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="11" t="s">
         <v>46</v>
       </c>
@@ -3538,19 +3656,19 @@
       <c r="N39" s="13"/>
       <c r="O39" s="12"/>
       <c r="P39" s="13"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="47"/>
-      <c r="S39" s="47"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="49"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="49"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
     </row>
     <row r="40" spans="1:26" s="6" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A40" s="47"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="11" t="s">
         <v>47</v>
       </c>
@@ -3572,68 +3690,68 @@
       <c r="N40" s="13"/>
       <c r="O40" s="12"/>
       <c r="P40" s="13"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="47"/>
-      <c r="S40" s="47"/>
-      <c r="T40" s="47"/>
-      <c r="U40" s="47"/>
-      <c r="V40" s="47"/>
-      <c r="W40" s="47"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="49"/>
+      <c r="S40" s="49"/>
+      <c r="T40" s="49"/>
+      <c r="U40" s="49"/>
+      <c r="V40" s="49"/>
+      <c r="W40" s="49"/>
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
     </row>
     <row r="41" spans="1:26" s="6" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A41" s="47"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="47"/>
-      <c r="K41" s="47"/>
-      <c r="L41" s="47"/>
-      <c r="M41" s="47"/>
-      <c r="N41" s="47"/>
-      <c r="O41" s="47"/>
-      <c r="P41" s="47"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
+      <c r="P41" s="49"/>
       <c r="Q41" s="7"/>
-      <c r="R41" s="47"/>
-      <c r="S41" s="47"/>
-      <c r="T41" s="47"/>
-      <c r="U41" s="47"/>
-      <c r="V41" s="47"/>
+      <c r="R41" s="49"/>
+      <c r="S41" s="49"/>
+      <c r="T41" s="49"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="49"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
     </row>
     <row r="42" spans="1:26" s="6" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A42" s="47"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="49"/>
+      <c r="P42" s="49"/>
       <c r="Q42" s="7"/>
-      <c r="R42" s="47"/>
+      <c r="R42" s="49"/>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
-      <c r="V42" s="47"/>
+      <c r="V42" s="49"/>
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
@@ -3646,40 +3764,40 @@
       <c r="B43" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="D43" s="59"/>
-      <c r="E43" s="58">
+      <c r="D43" s="62"/>
+      <c r="E43" s="61">
         <v>16</v>
       </c>
-      <c r="F43" s="59"/>
-      <c r="G43" s="58" t="s">
+      <c r="F43" s="62"/>
+      <c r="G43" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="H43" s="59"/>
-      <c r="I43" s="58">
+      <c r="H43" s="62"/>
+      <c r="I43" s="61">
         <v>18</v>
       </c>
-      <c r="J43" s="59"/>
-      <c r="K43" s="58" t="s">
+      <c r="J43" s="62"/>
+      <c r="K43" s="61" t="s">
         <v>79</v>
       </c>
-      <c r="L43" s="59"/>
-      <c r="M43" s="58">
+      <c r="L43" s="62"/>
+      <c r="M43" s="61">
         <v>20</v>
       </c>
-      <c r="N43" s="59"/>
-      <c r="O43" s="58" t="s">
+      <c r="N43" s="62"/>
+      <c r="O43" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="P43" s="59"/>
+      <c r="P43" s="62"/>
       <c r="Q43" s="7"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="47"/>
-      <c r="V43" s="47"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="49"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="49"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
@@ -3692,28 +3810,28 @@
       <c r="B44" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="56"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="56"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="56"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="48" t="s">
+      <c r="C44" s="59"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="60"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="59"/>
+      <c r="P44" s="60"/>
+      <c r="Q44" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="R44" s="47"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="47"/>
-      <c r="V44" s="47"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="49"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="49"/>
       <c r="W44" s="7"/>
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
@@ -3744,12 +3862,12 @@
       <c r="P45" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="49"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="49"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -3768,13 +3886,13 @@
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="47"/>
+      <c r="G46" s="49"/>
       <c r="H46" s="13"/>
       <c r="I46" s="14"/>
       <c r="J46" s="13"/>
-      <c r="K46" s="47"/>
+      <c r="K46" s="49"/>
       <c r="L46" s="13"/>
-      <c r="M46" s="47" t="s">
+      <c r="M46" s="49" t="s">
         <v>82</v>
       </c>
       <c r="N46" s="13" t="s">
@@ -3782,12 +3900,12 @@
       </c>
       <c r="O46" s="14"/>
       <c r="P46" s="13"/>
-      <c r="Q46" s="49"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-      <c r="V46" s="47"/>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="49"/>
+      <c r="S46" s="49"/>
+      <c r="T46" s="49"/>
+      <c r="U46" s="49"/>
+      <c r="V46" s="49"/>
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
@@ -3812,12 +3930,12 @@
       <c r="N47" s="13"/>
       <c r="O47" s="12"/>
       <c r="P47" s="13"/>
-      <c r="Q47" s="49"/>
-      <c r="R47" s="47"/>
-      <c r="S47" s="47"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="49"/>
+      <c r="S47" s="49"/>
       <c r="T47" s="32"/>
-      <c r="U47" s="47"/>
-      <c r="V47" s="47"/>
+      <c r="U47" s="49"/>
+      <c r="V47" s="49"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
@@ -3826,26 +3944,26 @@
     <row r="48" spans="1:26" s="6" customFormat="1" ht="17.25">
       <c r="A48" s="8"/>
       <c r="B48" s="16"/>
-      <c r="C48" s="60"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="60"/>
-      <c r="F48" s="60"/>
-      <c r="G48" s="60"/>
-      <c r="H48" s="60"/>
-      <c r="I48" s="60"/>
-      <c r="J48" s="60"/>
-      <c r="K48" s="60"/>
-      <c r="L48" s="60"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="60"/>
-      <c r="O48" s="60"/>
-      <c r="P48" s="61"/>
-      <c r="Q48" s="49"/>
-      <c r="R48" s="47"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="63"/>
+      <c r="P48" s="64"/>
+      <c r="Q48" s="52"/>
+      <c r="R48" s="49"/>
       <c r="S48" s="10"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="47"/>
-      <c r="V48" s="47"/>
+      <c r="T48" s="49"/>
+      <c r="U48" s="49"/>
+      <c r="V48" s="49"/>
       <c r="W48" s="7"/>
       <c r="X48" s="7"/>
       <c r="Y48" s="7"/>
@@ -3896,14 +4014,14 @@
         <v>89</v>
       </c>
       <c r="P49" s="13"/>
-      <c r="Q49" s="49"/>
-      <c r="R49" s="46" t="s">
+      <c r="Q49" s="52"/>
+      <c r="R49" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="47"/>
-      <c r="V49" s="47"/>
+      <c r="S49" s="49"/>
+      <c r="T49" s="49"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="49"/>
       <c r="W49" s="7"/>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
@@ -3938,14 +4056,14 @@
       <c r="P50" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q50" s="49"/>
-      <c r="R50" s="47" t="s">
+      <c r="Q50" s="52"/>
+      <c r="R50" s="49" t="s">
         <v>94</v>
       </c>
       <c r="S50" s="31"/>
-      <c r="T50" s="47"/>
+      <c r="T50" s="49"/>
       <c r="U50" s="17"/>
-      <c r="V50" s="47"/>
+      <c r="V50" s="49"/>
       <c r="W50" s="7"/>
       <c r="X50" s="7"/>
       <c r="Y50" s="7"/>
@@ -3976,23 +4094,23 @@
       <c r="P51" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q51" s="49"/>
-      <c r="R51" s="47" t="s">
+      <c r="Q51" s="52"/>
+      <c r="R51" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="S51" s="47" t="s">
+      <c r="S51" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="T51" s="47"/>
-      <c r="U51" s="47"/>
-      <c r="V51" s="47"/>
+      <c r="T51" s="49"/>
+      <c r="U51" s="49"/>
+      <c r="V51" s="49"/>
       <c r="W51" s="7"/>
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
     </row>
     <row r="52" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A52" s="47"/>
+      <c r="A52" s="49"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12"/>
       <c r="D52" s="13"/>
@@ -4014,16 +4132,16 @@
         <v>100</v>
       </c>
       <c r="P52" s="13"/>
-      <c r="Q52" s="49"/>
-      <c r="R52" s="47" t="s">
+      <c r="Q52" s="52"/>
+      <c r="R52" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="S52" s="47" t="s">
+      <c r="S52" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="T52" s="47"/>
-      <c r="U52" s="47"/>
-      <c r="V52" s="47"/>
+      <c r="T52" s="49"/>
+      <c r="U52" s="49"/>
+      <c r="V52" s="49"/>
       <c r="W52" s="7"/>
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
@@ -4048,16 +4166,16 @@
         <v>103</v>
       </c>
       <c r="P53" s="13"/>
-      <c r="Q53" s="49"/>
-      <c r="R53" s="47" t="s">
+      <c r="Q53" s="52"/>
+      <c r="R53" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="S53" s="47" t="s">
+      <c r="S53" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="T53" s="47"/>
+      <c r="T53" s="49"/>
       <c r="U53" s="17"/>
-      <c r="V53" s="47"/>
+      <c r="V53" s="49"/>
       <c r="W53" s="7"/>
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
@@ -4080,16 +4198,16 @@
       <c r="N54" s="13"/>
       <c r="O54" s="12"/>
       <c r="P54" s="13"/>
-      <c r="Q54" s="49"/>
-      <c r="R54" s="47" t="s">
+      <c r="Q54" s="52"/>
+      <c r="R54" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="S54" s="47" t="s">
+      <c r="S54" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="T54" s="47"/>
-      <c r="U54" s="47"/>
-      <c r="V54" s="47"/>
+      <c r="T54" s="49"/>
+      <c r="U54" s="49"/>
+      <c r="V54" s="49"/>
       <c r="W54" s="7"/>
       <c r="X54" s="7"/>
       <c r="Y54" s="7"/>
@@ -4112,23 +4230,23 @@
       <c r="N55" s="13"/>
       <c r="O55" s="12"/>
       <c r="P55" s="13"/>
-      <c r="Q55" s="49"/>
-      <c r="R55" s="47" t="s">
+      <c r="Q55" s="52"/>
+      <c r="R55" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="S55" s="47" t="s">
+      <c r="S55" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="T55" s="47"/>
-      <c r="U55" s="47"/>
-      <c r="V55" s="47"/>
+      <c r="T55" s="49"/>
+      <c r="U55" s="49"/>
+      <c r="V55" s="49"/>
       <c r="W55" s="7"/>
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
     </row>
     <row r="56" spans="1:26" s="6" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="49"/>
       <c r="B56" s="11"/>
       <c r="C56" s="19"/>
       <c r="D56" s="13"/>
@@ -4144,14 +4262,14 @@
       <c r="N56" s="13"/>
       <c r="O56" s="19"/>
       <c r="P56" s="13"/>
-      <c r="Q56" s="49"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47" t="s">
+      <c r="Q56" s="52"/>
+      <c r="R56" s="49"/>
+      <c r="S56" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="T56" s="47"/>
-      <c r="U56" s="47"/>
-      <c r="V56" s="47"/>
+      <c r="T56" s="49"/>
+      <c r="U56" s="49"/>
+      <c r="V56" s="49"/>
       <c r="W56" s="7"/>
       <c r="X56" s="7"/>
       <c r="Y56" s="7"/>
@@ -4174,14 +4292,14 @@
       <c r="N57" s="13"/>
       <c r="O57" s="12"/>
       <c r="P57" s="13"/>
-      <c r="Q57" s="49"/>
-      <c r="R57" s="47"/>
-      <c r="S57" s="47" t="s">
+      <c r="Q57" s="52"/>
+      <c r="R57" s="49"/>
+      <c r="S57" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="T57" s="47"/>
-      <c r="U57" s="47"/>
-      <c r="V57" s="47"/>
+      <c r="T57" s="49"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="49"/>
       <c r="W57" s="7"/>
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
@@ -4204,45 +4322,45 @@
       <c r="N58" s="13"/>
       <c r="O58" s="12"/>
       <c r="P58" s="13"/>
-      <c r="Q58" s="49"/>
-      <c r="R58" s="47"/>
-      <c r="S58" s="47" t="s">
+      <c r="Q58" s="52"/>
+      <c r="R58" s="49"/>
+      <c r="S58" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="T58" s="47"/>
-      <c r="U58" s="47"/>
-      <c r="V58" s="47"/>
+      <c r="T58" s="49"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="49"/>
     </row>
     <row r="59" spans="1:26" ht="30.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="52"/>
-      <c r="D59" s="53"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="53"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="55"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="54"/>
-      <c r="L59" s="55"/>
-      <c r="M59" s="54"/>
-      <c r="N59" s="55"/>
-      <c r="O59" s="54"/>
-      <c r="P59" s="55"/>
-      <c r="Q59" s="49"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="47" t="s">
+      <c r="C59" s="55"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="58"/>
+      <c r="K59" s="57"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="57"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="57"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="49"/>
+      <c r="S59" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="T59" s="47"/>
-      <c r="U59" s="47"/>
-      <c r="V59" s="47"/>
+      <c r="T59" s="49"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="49"/>
     </row>
     <row r="60" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A60" s="47"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="11" t="s">
         <v>46</v>
       </c>
@@ -4260,17 +4378,17 @@
       <c r="N60" s="13"/>
       <c r="O60" s="12"/>
       <c r="P60" s="13"/>
-      <c r="Q60" s="49"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="47" t="s">
+      <c r="Q60" s="52"/>
+      <c r="R60" s="49"/>
+      <c r="S60" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="T60" s="47"/>
-      <c r="U60" s="47"/>
-      <c r="V60" s="47"/>
+      <c r="T60" s="49"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="49"/>
     </row>
     <row r="61" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A61" s="47"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="11" t="s">
         <v>47</v>
       </c>
@@ -4288,8 +4406,8 @@
       <c r="N61" s="13"/>
       <c r="O61" s="12"/>
       <c r="P61" s="13"/>
-      <c r="Q61" s="49"/>
-      <c r="R61" s="47"/>
+      <c r="Q61" s="52"/>
+      <c r="R61" s="49"/>
       <c r="S61" s="33" t="s">
         <v>115</v>
       </c>
@@ -4298,50 +4416,50 @@
       <c r="V61" s="7"/>
     </row>
     <row r="62" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A62" s="47"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="47"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="47"/>
-      <c r="G62" s="47"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="47"/>
-      <c r="J62" s="47"/>
-      <c r="K62" s="47"/>
-      <c r="L62" s="47"/>
-      <c r="M62" s="47"/>
-      <c r="N62" s="47"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="47"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="49"/>
+      <c r="M62" s="49"/>
+      <c r="N62" s="49"/>
+      <c r="O62" s="49"/>
+      <c r="P62" s="49"/>
+      <c r="Q62" s="49"/>
+      <c r="R62" s="49"/>
+      <c r="S62" s="49"/>
       <c r="T62" s="7"/>
       <c r="U62" s="7"/>
       <c r="V62" s="7"/>
     </row>
     <row r="63" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A63" s="47"/>
-      <c r="B63" s="47"/>
-      <c r="C63" s="47"/>
-      <c r="D63" s="47"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="47"/>
-      <c r="G63" s="47"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="47"/>
-      <c r="J63" s="47"/>
-      <c r="K63" s="47"/>
-      <c r="L63" s="47"/>
-      <c r="M63" s="47"/>
-      <c r="N63" s="47"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="47"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="47"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="49"/>
+      <c r="N63" s="49"/>
+      <c r="O63" s="49"/>
+      <c r="P63" s="49"/>
+      <c r="Q63" s="49"/>
+      <c r="R63" s="49"/>
+      <c r="S63" s="49"/>
+      <c r="T63" s="49"/>
       <c r="U63" s="17"/>
       <c r="V63" s="7"/>
     </row>
@@ -4352,38 +4470,38 @@
       <c r="B64" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C64" s="58">
+      <c r="C64" s="61">
         <v>22</v>
       </c>
-      <c r="D64" s="59"/>
-      <c r="E64" s="58" t="s">
+      <c r="D64" s="62"/>
+      <c r="E64" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="F64" s="59"/>
-      <c r="G64" s="58">
+      <c r="F64" s="62"/>
+      <c r="G64" s="61">
         <v>24</v>
       </c>
-      <c r="H64" s="59"/>
-      <c r="I64" s="58">
+      <c r="H64" s="62"/>
+      <c r="I64" s="61">
         <v>25</v>
       </c>
-      <c r="J64" s="59"/>
-      <c r="K64" s="58">
+      <c r="J64" s="62"/>
+      <c r="K64" s="61">
         <v>26</v>
       </c>
-      <c r="L64" s="59"/>
-      <c r="M64" s="58">
+      <c r="L64" s="62"/>
+      <c r="M64" s="61">
         <v>27</v>
       </c>
-      <c r="N64" s="59"/>
-      <c r="O64" s="58">
+      <c r="N64" s="62"/>
+      <c r="O64" s="61">
         <v>28</v>
       </c>
-      <c r="P64" s="59"/>
-      <c r="Q64" s="47"/>
-      <c r="R64" s="47"/>
+      <c r="P64" s="62"/>
+      <c r="Q64" s="49"/>
+      <c r="R64" s="49"/>
       <c r="S64" s="34"/>
-      <c r="T64" s="47"/>
+      <c r="T64" s="49"/>
       <c r="U64" s="17"/>
       <c r="V64" s="7"/>
     </row>
@@ -4394,26 +4512,26 @@
       <c r="B65" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="56"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="56"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="56"/>
-      <c r="L65" s="57"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="57"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="57"/>
-      <c r="Q65" s="48" t="s">
+      <c r="C65" s="59"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="59"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="59"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="59"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="59"/>
+      <c r="P65" s="60"/>
+      <c r="Q65" s="51" t="s">
         <v>117</v>
       </c>
-      <c r="R65" s="47"/>
+      <c r="R65" s="49"/>
       <c r="S65" s="34"/>
-      <c r="T65" s="47"/>
+      <c r="T65" s="49"/>
       <c r="U65" s="17"/>
       <c r="V65" s="7"/>
     </row>
@@ -4446,10 +4564,10 @@
       <c r="N66" s="13"/>
       <c r="O66" s="14"/>
       <c r="P66" s="13"/>
-      <c r="Q66" s="49"/>
-      <c r="R66" s="47"/>
+      <c r="Q66" s="52"/>
+      <c r="R66" s="49"/>
       <c r="S66" s="34"/>
-      <c r="T66" s="47"/>
+      <c r="T66" s="49"/>
       <c r="U66" s="17"/>
       <c r="V66" s="7"/>
     </row>
@@ -4458,17 +4576,17 @@
       <c r="B67" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="47"/>
+      <c r="C67" s="49"/>
       <c r="D67" s="13"/>
       <c r="E67" s="14"/>
       <c r="F67" s="13"/>
-      <c r="G67" s="47" t="s">
+      <c r="G67" s="49" t="s">
         <v>17</v>
       </c>
       <c r="H67" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I67" s="47" t="s">
+      <c r="I67" s="49" t="s">
         <v>17</v>
       </c>
       <c r="J67" s="13" t="s">
@@ -4480,8 +4598,8 @@
       <c r="N67" s="13"/>
       <c r="O67" s="14"/>
       <c r="P67" s="13"/>
-      <c r="Q67" s="49"/>
-      <c r="R67" s="47"/>
+      <c r="Q67" s="52"/>
+      <c r="R67" s="49"/>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
@@ -4506,8 +4624,8 @@
       <c r="N68" s="13"/>
       <c r="O68" s="12"/>
       <c r="P68" s="13"/>
-      <c r="Q68" s="49"/>
-      <c r="R68" s="47"/>
+      <c r="Q68" s="52"/>
+      <c r="R68" s="49"/>
       <c r="S68" s="7"/>
       <c r="T68" s="7"/>
       <c r="U68" s="7"/>
@@ -4518,22 +4636,22 @@
       <c r="B69" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="60"/>
-      <c r="F69" s="60"/>
-      <c r="G69" s="60"/>
-      <c r="H69" s="60"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="60"/>
-      <c r="K69" s="60"/>
-      <c r="L69" s="60"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="60"/>
-      <c r="O69" s="60"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="49"/>
-      <c r="R69" s="47"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="63"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="63"/>
+      <c r="P69" s="64"/>
+      <c r="Q69" s="52"/>
+      <c r="R69" s="49"/>
       <c r="S69" s="7"/>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
@@ -4580,9 +4698,9 @@
       <c r="P70" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q70" s="49"/>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47"/>
+      <c r="Q70" s="52"/>
+      <c r="R70" s="49"/>
+      <c r="S70" s="49"/>
       <c r="T70" s="7"/>
       <c r="U70" s="7"/>
       <c r="V70" s="7"/>
@@ -4618,9 +4736,9 @@
       </c>
       <c r="O71" s="12"/>
       <c r="P71" s="13"/>
-      <c r="Q71" s="49"/>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47"/>
+      <c r="Q71" s="52"/>
+      <c r="R71" s="49"/>
+      <c r="S71" s="49"/>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
@@ -4654,15 +4772,15 @@
       <c r="P72" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q72" s="49"/>
-      <c r="R72" s="47"/>
-      <c r="S72" s="47"/>
+      <c r="Q72" s="52"/>
+      <c r="R72" s="49"/>
+      <c r="S72" s="49"/>
       <c r="T72" s="7"/>
       <c r="U72" s="7"/>
       <c r="V72" s="7"/>
     </row>
     <row r="73" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A73" s="47"/>
+      <c r="A73" s="49"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
       <c r="D73" s="13"/>
@@ -4690,9 +4808,9 @@
       <c r="P73" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q73" s="49"/>
-      <c r="R73" s="47"/>
-      <c r="S73" s="47"/>
+      <c r="Q73" s="52"/>
+      <c r="R73" s="49"/>
+      <c r="S73" s="49"/>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -4718,9 +4836,9 @@
       </c>
       <c r="O74" s="12"/>
       <c r="P74" s="13"/>
-      <c r="Q74" s="49"/>
-      <c r="R74" s="47"/>
-      <c r="S74" s="47"/>
+      <c r="Q74" s="52"/>
+      <c r="R74" s="49"/>
+      <c r="S74" s="49"/>
       <c r="T74" s="7"/>
       <c r="U74" s="35"/>
       <c r="V74" s="7"/>
@@ -4746,9 +4864,9 @@
       </c>
       <c r="O75" s="12"/>
       <c r="P75" s="13"/>
-      <c r="Q75" s="49"/>
-      <c r="R75" s="47"/>
-      <c r="S75" s="47"/>
+      <c r="Q75" s="52"/>
+      <c r="R75" s="49"/>
+      <c r="S75" s="49"/>
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
@@ -4770,15 +4888,15 @@
       <c r="N76" s="13"/>
       <c r="O76" s="12"/>
       <c r="P76" s="13"/>
-      <c r="Q76" s="49"/>
-      <c r="R76" s="47"/>
-      <c r="S76" s="47"/>
+      <c r="Q76" s="52"/>
+      <c r="R76" s="49"/>
+      <c r="S76" s="49"/>
       <c r="T76" s="7"/>
       <c r="U76" s="7"/>
       <c r="V76" s="7"/>
     </row>
     <row r="77" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A77" s="47"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="11"/>
       <c r="C77" s="19"/>
       <c r="D77" s="13"/>
@@ -4794,7 +4912,7 @@
       <c r="N77" s="13"/>
       <c r="O77" s="19"/>
       <c r="P77" s="13"/>
-      <c r="Q77" s="49"/>
+      <c r="Q77" s="52"/>
       <c r="R77" s="7"/>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
@@ -4818,7 +4936,7 @@
       <c r="N78" s="13"/>
       <c r="O78" s="12"/>
       <c r="P78" s="13"/>
-      <c r="Q78" s="49"/>
+      <c r="Q78" s="52"/>
       <c r="R78" s="7"/>
       <c r="S78" s="7"/>
       <c r="T78" s="7"/>
@@ -4842,8 +4960,8 @@
       <c r="N79" s="13"/>
       <c r="O79" s="12"/>
       <c r="P79" s="13"/>
-      <c r="Q79" s="49"/>
-      <c r="R79" s="47"/>
+      <c r="Q79" s="52"/>
+      <c r="R79" s="49"/>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
       <c r="U79" s="7"/>
@@ -4854,29 +4972,29 @@
       <c r="B80" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="52"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="54"/>
-      <c r="H80" s="55"/>
-      <c r="I80" s="54"/>
-      <c r="J80" s="55"/>
-      <c r="K80" s="54"/>
-      <c r="L80" s="55"/>
-      <c r="M80" s="54"/>
-      <c r="N80" s="55"/>
-      <c r="O80" s="54"/>
-      <c r="P80" s="55"/>
-      <c r="Q80" s="49"/>
-      <c r="R80" s="47"/>
-      <c r="S80" s="47"/>
-      <c r="T80" s="47"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="58"/>
+      <c r="I80" s="57"/>
+      <c r="J80" s="58"/>
+      <c r="K80" s="57"/>
+      <c r="L80" s="58"/>
+      <c r="M80" s="57"/>
+      <c r="N80" s="58"/>
+      <c r="O80" s="57"/>
+      <c r="P80" s="58"/>
+      <c r="Q80" s="52"/>
+      <c r="R80" s="49"/>
+      <c r="S80" s="49"/>
+      <c r="T80" s="49"/>
       <c r="U80" s="7"/>
       <c r="V80" s="7"/>
     </row>
     <row r="81" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A81" s="47"/>
+      <c r="A81" s="49"/>
       <c r="B81" s="11" t="s">
         <v>46</v>
       </c>
@@ -4894,15 +5012,15 @@
       <c r="N81" s="13"/>
       <c r="O81" s="12"/>
       <c r="P81" s="13"/>
-      <c r="Q81" s="49"/>
-      <c r="R81" s="47"/>
-      <c r="S81" s="47"/>
-      <c r="T81" s="47"/>
+      <c r="Q81" s="52"/>
+      <c r="R81" s="49"/>
+      <c r="S81" s="49"/>
+      <c r="T81" s="49"/>
       <c r="U81" s="7"/>
       <c r="V81" s="7"/>
     </row>
     <row r="82" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A82" s="47"/>
+      <c r="A82" s="49"/>
       <c r="B82" s="11" t="s">
         <v>47</v>
       </c>
@@ -4920,49 +5038,49 @@
       <c r="N82" s="13"/>
       <c r="O82" s="12"/>
       <c r="P82" s="13"/>
-      <c r="Q82" s="49"/>
-      <c r="R82" s="47"/>
-      <c r="S82" s="47"/>
-      <c r="T82" s="47"/>
+      <c r="Q82" s="52"/>
+      <c r="R82" s="49"/>
+      <c r="S82" s="49"/>
+      <c r="T82" s="49"/>
       <c r="U82" s="7"/>
       <c r="V82" s="7"/>
     </row>
     <row r="83" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A83" s="47"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
-      <c r="D83" s="47"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="47"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="47"/>
-      <c r="I83" s="47"/>
-      <c r="J83" s="47"/>
-      <c r="K83" s="47"/>
-      <c r="L83" s="47"/>
-      <c r="M83" s="47"/>
-      <c r="N83" s="47"/>
-      <c r="O83" s="47"/>
-      <c r="P83" s="47"/>
-      <c r="Q83" s="47"/>
-      <c r="R83" s="47"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="49"/>
+      <c r="H83" s="49"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="49"/>
+      <c r="K83" s="49"/>
+      <c r="L83" s="49"/>
+      <c r="M83" s="49"/>
+      <c r="N83" s="49"/>
+      <c r="O83" s="49"/>
+      <c r="P83" s="49"/>
+      <c r="Q83" s="49"/>
+      <c r="R83" s="49"/>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
       <c r="U83" s="7"/>
       <c r="V83" s="7"/>
     </row>
     <row r="84" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A84" s="47"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="47"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="47"/>
-      <c r="K84" s="47"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
@@ -4981,21 +5099,21 @@
       <c r="B85" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="58">
+      <c r="C85" s="61">
         <v>29</v>
       </c>
-      <c r="D85" s="59"/>
-      <c r="E85" s="58">
+      <c r="D85" s="62"/>
+      <c r="E85" s="61">
         <v>30</v>
       </c>
-      <c r="F85" s="59"/>
-      <c r="G85" s="58" t="s">
+      <c r="F85" s="62"/>
+      <c r="G85" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="H85" s="59"/>
-      <c r="I85" s="47"/>
-      <c r="J85" s="47"/>
-      <c r="K85" s="47"/>
+      <c r="H85" s="62"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+      <c r="K85" s="49"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
@@ -5014,21 +5132,21 @@
       <c r="B86" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C86" s="56"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="56"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="56"/>
-      <c r="H86" s="57"/>
-      <c r="I86" s="47"/>
-      <c r="J86" s="47"/>
-      <c r="K86" s="47"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="60"/>
+      <c r="I86" s="49"/>
+      <c r="J86" s="49"/>
+      <c r="K86" s="49"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
       <c r="O86" s="7"/>
       <c r="P86" s="7"/>
-      <c r="Q86" s="48" t="s">
+      <c r="Q86" s="51" t="s">
         <v>135</v>
       </c>
       <c r="R86" s="7"/>
@@ -5050,15 +5168,15 @@
       <c r="F87" s="13"/>
       <c r="G87" s="14"/>
       <c r="H87" s="13"/>
-      <c r="I87" s="47"/>
-      <c r="J87" s="47"/>
-      <c r="K87" s="47"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="49"/>
+      <c r="K87" s="49"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
       <c r="O87" s="7"/>
       <c r="P87" s="7"/>
-      <c r="Q87" s="49"/>
+      <c r="Q87" s="52"/>
       <c r="R87" s="7"/>
       <c r="S87" s="7"/>
       <c r="T87" s="7"/>
@@ -5072,23 +5190,23 @@
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="13"/>
-      <c r="E88" s="47"/>
+      <c r="E88" s="49"/>
       <c r="F88" s="13"/>
-      <c r="G88" s="47" t="s">
+      <c r="G88" s="49" t="s">
         <v>136</v>
       </c>
       <c r="H88" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I88" s="47"/>
-      <c r="J88" s="47"/>
-      <c r="K88" s="47"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
       <c r="O88" s="7"/>
       <c r="P88" s="7"/>
-      <c r="Q88" s="49"/>
+      <c r="Q88" s="52"/>
       <c r="R88" s="7"/>
       <c r="S88" s="7"/>
       <c r="T88" s="7"/>
@@ -5106,15 +5224,15 @@
       <c r="F89" s="13"/>
       <c r="G89" s="12"/>
       <c r="H89" s="13"/>
-      <c r="I89" s="47"/>
-      <c r="J89" s="47"/>
-      <c r="K89" s="47"/>
+      <c r="I89" s="49"/>
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
       <c r="O89" s="7"/>
       <c r="P89" s="7"/>
-      <c r="Q89" s="49"/>
+      <c r="Q89" s="52"/>
       <c r="R89" s="7"/>
       <c r="S89" s="7"/>
       <c r="T89" s="7"/>
@@ -5126,21 +5244,21 @@
       <c r="B90" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="60"/>
-      <c r="D90" s="60"/>
-      <c r="E90" s="60"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="54"/>
-      <c r="H90" s="55"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="47"/>
-      <c r="K90" s="47"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="58"/>
+      <c r="I90" s="49"/>
+      <c r="J90" s="49"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
       <c r="O90" s="7"/>
       <c r="P90" s="7"/>
-      <c r="Q90" s="49"/>
+      <c r="Q90" s="52"/>
       <c r="R90" s="7"/>
       <c r="S90" s="7"/>
       <c r="T90" s="7"/>
@@ -5170,9 +5288,9 @@
       <c r="H91" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I91" s="47"/>
-      <c r="J91" s="47"/>
-      <c r="K91" s="47"/>
+      <c r="I91" s="49"/>
+      <c r="J91" s="49"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
@@ -5180,7 +5298,7 @@
         <v>140</v>
       </c>
       <c r="P91" s="7"/>
-      <c r="Q91" s="49"/>
+      <c r="Q91" s="52"/>
       <c r="R91" s="7"/>
       <c r="S91" s="7"/>
       <c r="T91" s="7"/>
@@ -5198,15 +5316,15 @@
         <v>141</v>
       </c>
       <c r="H92" s="13"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="47"/>
-      <c r="K92" s="47"/>
+      <c r="I92" s="49"/>
+      <c r="J92" s="49"/>
+      <c r="K92" s="49"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
       <c r="O92" s="7"/>
       <c r="P92" s="7"/>
-      <c r="Q92" s="49"/>
+      <c r="Q92" s="52"/>
       <c r="R92" s="7"/>
       <c r="S92" s="7"/>
       <c r="T92" s="7"/>
@@ -5228,15 +5346,15 @@
       <c r="H93" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I93" s="47"/>
-      <c r="J93" s="47"/>
-      <c r="K93" s="47"/>
+      <c r="I93" s="49"/>
+      <c r="J93" s="49"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
       <c r="O93" s="7"/>
       <c r="P93" s="7"/>
-      <c r="Q93" s="49"/>
+      <c r="Q93" s="52"/>
       <c r="R93" s="7"/>
       <c r="S93" s="7"/>
       <c r="T93" s="7"/>
@@ -5244,7 +5362,7 @@
       <c r="V93" s="7"/>
     </row>
     <row r="94" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A94" s="47"/>
+      <c r="A94" s="49"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12"/>
       <c r="D94" s="13"/>
@@ -5256,15 +5374,15 @@
       </c>
       <c r="G94" s="12"/>
       <c r="H94" s="13"/>
-      <c r="I94" s="47"/>
-      <c r="J94" s="47"/>
-      <c r="K94" s="47"/>
+      <c r="I94" s="49"/>
+      <c r="J94" s="49"/>
+      <c r="K94" s="49"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
       <c r="O94" s="7"/>
       <c r="P94" s="7"/>
-      <c r="Q94" s="49"/>
+      <c r="Q94" s="52"/>
       <c r="R94" s="7"/>
       <c r="S94" s="7"/>
       <c r="T94" s="7"/>
@@ -5288,15 +5406,15 @@
       <c r="H95" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I95" s="47"/>
-      <c r="J95" s="47"/>
-      <c r="K95" s="47"/>
+      <c r="I95" s="49"/>
+      <c r="J95" s="49"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
       <c r="O95" s="7"/>
       <c r="P95" s="7"/>
-      <c r="Q95" s="49"/>
+      <c r="Q95" s="52"/>
       <c r="R95" s="7"/>
       <c r="S95" s="7"/>
       <c r="T95" s="7"/>
@@ -5316,15 +5434,15 @@
       </c>
       <c r="G96" s="12"/>
       <c r="H96" s="13"/>
-      <c r="I96" s="47"/>
-      <c r="J96" s="47"/>
-      <c r="K96" s="47"/>
+      <c r="I96" s="49"/>
+      <c r="J96" s="49"/>
+      <c r="K96" s="49"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
       <c r="O96" s="7"/>
       <c r="P96" s="7"/>
-      <c r="Q96" s="49"/>
+      <c r="Q96" s="52"/>
       <c r="R96" s="7"/>
       <c r="S96" s="7"/>
       <c r="T96" s="7"/>
@@ -5342,15 +5460,15 @@
       <c r="F97" s="13"/>
       <c r="G97" s="12"/>
       <c r="H97" s="13"/>
-      <c r="I97" s="47"/>
-      <c r="J97" s="47"/>
-      <c r="K97" s="47"/>
+      <c r="I97" s="49"/>
+      <c r="J97" s="49"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
       <c r="O97" s="7"/>
       <c r="P97" s="7"/>
-      <c r="Q97" s="49"/>
+      <c r="Q97" s="52"/>
       <c r="R97" s="7"/>
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
@@ -5358,7 +5476,7 @@
       <c r="V97" s="7"/>
     </row>
     <row r="98" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A98" s="47"/>
+      <c r="A98" s="49"/>
       <c r="B98" s="11"/>
       <c r="C98" s="19"/>
       <c r="D98" s="13"/>
@@ -5368,15 +5486,15 @@
       <c r="F98" s="13"/>
       <c r="G98" s="12"/>
       <c r="H98" s="13"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="47"/>
-      <c r="K98" s="47"/>
+      <c r="I98" s="49"/>
+      <c r="J98" s="49"/>
+      <c r="K98" s="49"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
       <c r="O98" s="7"/>
       <c r="P98" s="7"/>
-      <c r="Q98" s="49"/>
+      <c r="Q98" s="52"/>
       <c r="R98" s="7"/>
       <c r="S98" s="7"/>
       <c r="T98" s="7"/>
@@ -5392,15 +5510,15 @@
       <c r="F99" s="13"/>
       <c r="G99" s="12"/>
       <c r="H99" s="13"/>
-      <c r="I99" s="47"/>
-      <c r="J99" s="47"/>
-      <c r="K99" s="47"/>
+      <c r="I99" s="49"/>
+      <c r="J99" s="49"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
       <c r="O99" s="7"/>
       <c r="P99" s="7"/>
-      <c r="Q99" s="49"/>
+      <c r="Q99" s="52"/>
       <c r="R99" s="7"/>
       <c r="S99" s="7"/>
       <c r="T99" s="7"/>
@@ -5416,15 +5534,15 @@
       <c r="F100" s="13"/>
       <c r="G100" s="12"/>
       <c r="H100" s="13"/>
-      <c r="I100" s="47"/>
-      <c r="J100" s="47"/>
-      <c r="K100" s="47"/>
+      <c r="I100" s="49"/>
+      <c r="J100" s="49"/>
+      <c r="K100" s="49"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
       <c r="O100" s="7"/>
       <c r="P100" s="7"/>
-      <c r="Q100" s="49"/>
+      <c r="Q100" s="52"/>
       <c r="R100" s="7"/>
       <c r="S100" s="7"/>
       <c r="T100" s="7"/>
@@ -5436,21 +5554,21 @@
       <c r="B101" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C101" s="52"/>
-      <c r="D101" s="53"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="54"/>
-      <c r="H101" s="55"/>
-      <c r="I101" s="47"/>
-      <c r="J101" s="47"/>
-      <c r="K101" s="47"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="56"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="56"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="58"/>
+      <c r="I101" s="49"/>
+      <c r="J101" s="49"/>
+      <c r="K101" s="49"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
       <c r="O101" s="7"/>
       <c r="P101" s="7"/>
-      <c r="Q101" s="49"/>
+      <c r="Q101" s="52"/>
       <c r="R101" s="7"/>
       <c r="S101" s="7"/>
       <c r="T101" s="7"/>
@@ -5458,7 +5576,7 @@
       <c r="V101" s="7"/>
     </row>
     <row r="102" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A102" s="47"/>
+      <c r="A102" s="49"/>
       <c r="B102" s="11" t="s">
         <v>46</v>
       </c>
@@ -5468,15 +5586,15 @@
       <c r="F102" s="13"/>
       <c r="G102" s="12"/>
       <c r="H102" s="13"/>
-      <c r="I102" s="47"/>
-      <c r="J102" s="47"/>
-      <c r="K102" s="47"/>
+      <c r="I102" s="49"/>
+      <c r="J102" s="49"/>
+      <c r="K102" s="49"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
       <c r="O102" s="7"/>
       <c r="P102" s="7"/>
-      <c r="Q102" s="49"/>
+      <c r="Q102" s="52"/>
       <c r="R102" s="7"/>
       <c r="S102" s="7"/>
       <c r="T102" s="7"/>
@@ -5484,7 +5602,7 @@
       <c r="V102" s="7"/>
     </row>
     <row r="103" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A103" s="47"/>
+      <c r="A103" s="49"/>
       <c r="B103" s="11" t="s">
         <v>47</v>
       </c>
@@ -5494,15 +5612,15 @@
       <c r="F103" s="13"/>
       <c r="G103" s="12"/>
       <c r="H103" s="13"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="47"/>
-      <c r="K103" s="47"/>
+      <c r="I103" s="49"/>
+      <c r="J103" s="49"/>
+      <c r="K103" s="49"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
       <c r="O103" s="7"/>
       <c r="P103" s="7"/>
-      <c r="Q103" s="49"/>
+      <c r="Q103" s="52"/>
       <c r="R103" s="7"/>
       <c r="S103" s="7"/>
       <c r="T103" s="7"/>
@@ -5510,17 +5628,17 @@
       <c r="V103" s="7"/>
     </row>
     <row r="104" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A104" s="47"/>
-      <c r="B104" s="47"/>
-      <c r="C104" s="47"/>
-      <c r="D104" s="47"/>
-      <c r="E104" s="47"/>
-      <c r="F104" s="47"/>
-      <c r="G104" s="47"/>
-      <c r="H104" s="47"/>
-      <c r="I104" s="47"/>
-      <c r="J104" s="47"/>
-      <c r="K104" s="47"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49"/>
+      <c r="D104" s="49"/>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="49"/>
+      <c r="H104" s="49"/>
+      <c r="I104" s="49"/>
+      <c r="J104" s="49"/>
+      <c r="K104" s="49"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -5533,12 +5651,12 @@
       <c r="V104" s="7"/>
     </row>
     <row r="105" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A105" s="47"/>
-      <c r="B105" s="47"/>
-      <c r="C105" s="47"/>
-      <c r="D105" s="47"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="47"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="49"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
@@ -5556,12 +5674,12 @@
       <c r="V105" s="7"/>
     </row>
     <row r="106" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A106" s="47"/>
-      <c r="B106" s="47"/>
-      <c r="C106" s="47"/>
-      <c r="D106" s="47"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="47"/>
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="49"/>
+      <c r="D106" s="49"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
@@ -5579,17 +5697,17 @@
       <c r="V106" s="7"/>
     </row>
     <row r="107" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A107" s="47"/>
-      <c r="B107" s="47"/>
-      <c r="C107" s="47"/>
-      <c r="D107" s="47"/>
-      <c r="E107" s="47"/>
-      <c r="F107" s="47"/>
-      <c r="G107" s="47"/>
-      <c r="H107" s="47"/>
-      <c r="I107" s="47"/>
-      <c r="J107" s="47"/>
-      <c r="K107" s="47"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="49"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="49"/>
+      <c r="J107" s="49"/>
+      <c r="K107" s="49"/>
       <c r="L107" s="7"/>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
@@ -5602,17 +5720,17 @@
       <c r="V107" s="7"/>
     </row>
     <row r="108" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A108" s="47"/>
-      <c r="B108" s="47"/>
-      <c r="C108" s="47"/>
-      <c r="D108" s="47"/>
-      <c r="E108" s="47"/>
-      <c r="F108" s="47"/>
-      <c r="G108" s="47"/>
-      <c r="H108" s="47"/>
-      <c r="I108" s="47"/>
-      <c r="J108" s="47"/>
-      <c r="K108" s="47"/>
+      <c r="A108" s="49"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="49"/>
+      <c r="D108" s="49"/>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="49"/>
+      <c r="H108" s="49"/>
+      <c r="I108" s="49"/>
+      <c r="J108" s="49"/>
+      <c r="K108" s="49"/>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
@@ -5625,17 +5743,17 @@
       <c r="V108" s="7"/>
     </row>
     <row r="109" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A109" s="47"/>
-      <c r="B109" s="47"/>
-      <c r="C109" s="47"/>
-      <c r="D109" s="47"/>
-      <c r="E109" s="47"/>
-      <c r="F109" s="47"/>
-      <c r="G109" s="47"/>
-      <c r="H109" s="47"/>
-      <c r="I109" s="47"/>
-      <c r="J109" s="47"/>
-      <c r="K109" s="47"/>
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="49"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="49"/>
+      <c r="J109" s="49"/>
+      <c r="K109" s="49"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
@@ -5648,17 +5766,17 @@
       <c r="V109" s="7"/>
     </row>
     <row r="110" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A110" s="47"/>
-      <c r="B110" s="47"/>
-      <c r="C110" s="47"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="47"/>
-      <c r="G110" s="47"/>
-      <c r="H110" s="47"/>
-      <c r="I110" s="47"/>
-      <c r="J110" s="47"/>
-      <c r="K110" s="47"/>
+      <c r="A110" s="49"/>
+      <c r="B110" s="49"/>
+      <c r="C110" s="49"/>
+      <c r="D110" s="49"/>
+      <c r="E110" s="49"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="49"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="49"/>
+      <c r="J110" s="49"/>
+      <c r="K110" s="49"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -5671,17 +5789,17 @@
       <c r="V110" s="7"/>
     </row>
     <row r="111" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A111" s="47"/>
-      <c r="B111" s="47"/>
-      <c r="C111" s="47"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="47"/>
-      <c r="F111" s="47"/>
-      <c r="G111" s="47"/>
-      <c r="H111" s="47"/>
-      <c r="I111" s="47"/>
-      <c r="J111" s="47"/>
-      <c r="K111" s="47"/>
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
+      <c r="H111" s="49"/>
+      <c r="I111" s="49"/>
+      <c r="J111" s="49"/>
+      <c r="K111" s="49"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
@@ -5694,17 +5812,17 @@
       <c r="V111" s="7"/>
     </row>
     <row r="112" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A112" s="47"/>
-      <c r="B112" s="47"/>
-      <c r="C112" s="47"/>
-      <c r="D112" s="47"/>
-      <c r="E112" s="47"/>
-      <c r="F112" s="47"/>
-      <c r="G112" s="47"/>
-      <c r="H112" s="47"/>
-      <c r="I112" s="47"/>
-      <c r="J112" s="47"/>
-      <c r="K112" s="47"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="49"/>
+      <c r="D112" s="49"/>
+      <c r="E112" s="49"/>
+      <c r="F112" s="49"/>
+      <c r="G112" s="49"/>
+      <c r="H112" s="49"/>
+      <c r="I112" s="49"/>
+      <c r="J112" s="49"/>
+      <c r="K112" s="49"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -6072,34 +6190,34 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="63"/>
-      <c r="E1" s="62">
+      <c r="D1" s="66"/>
+      <c r="E1" s="65">
         <v>2</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="62" t="s">
+      <c r="F1" s="66"/>
+      <c r="G1" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="H1" s="63"/>
-      <c r="I1" s="62">
+      <c r="H1" s="66"/>
+      <c r="I1" s="65">
         <v>4</v>
       </c>
-      <c r="J1" s="63"/>
-      <c r="K1" s="62">
+      <c r="J1" s="66"/>
+      <c r="K1" s="65">
         <v>5</v>
       </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="62">
+      <c r="L1" s="66"/>
+      <c r="M1" s="65">
         <v>6</v>
       </c>
-      <c r="N1" s="63"/>
-      <c r="O1" s="62">
+      <c r="N1" s="66"/>
+      <c r="O1" s="65">
         <v>7</v>
       </c>
-      <c r="P1" s="63"/>
+      <c r="P1" s="66"/>
       <c r="Q1" s="2" t="s">
         <v>4</v>
       </c>
@@ -6113,9 +6231,9 @@
       <c r="U1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="47"/>
-      <c r="W1" s="47"/>
-      <c r="X1" s="47"/>
+      <c r="V1" s="49"/>
+      <c r="W1" s="49"/>
+      <c r="X1" s="49"/>
       <c r="Y1" s="7"/>
       <c r="Z1" s="7"/>
     </row>
@@ -6126,32 +6244,32 @@
       <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="64" t="s">
+      <c r="C2" s="59"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="60"/>
+      <c r="K2" s="59"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47" t="s">
+      <c r="R2" s="49"/>
+      <c r="S2" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="49"/>
       <c r="V2" s="10"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="49"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
     </row>
@@ -6168,24 +6286,32 @@
       <c r="F3" s="13"/>
       <c r="G3" s="14"/>
       <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
+      <c r="I3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="K3" s="14"/>
       <c r="L3" s="13"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="13"/>
+      <c r="M3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="O3" s="14"/>
       <c r="P3" s="13"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47" t="s">
+      <c r="Q3" s="54"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="47"/>
-      <c r="W3" s="47"/>
-      <c r="X3" s="47"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
     </row>
@@ -6202,30 +6328,36 @@
       </c>
       <c r="E4" s="14"/>
       <c r="F4" s="13"/>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="47"/>
+      <c r="H4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="49"/>
       <c r="J4" s="13"/>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="L4" s="13"/>
+      <c r="L4" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="M4" s="14"/>
       <c r="N4" s="13"/>
-      <c r="O4" s="47"/>
+      <c r="O4" s="49" t="s">
+        <v>153</v>
+      </c>
       <c r="P4" s="13"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47" t="s">
+      <c r="Q4" s="54"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="T4" s="47"/>
+      <c r="T4" s="49"/>
       <c r="U4" s="15"/>
       <c r="V4" s="7"/>
       <c r="W4" s="7"/>
-      <c r="X4" s="47"/>
+      <c r="X4" s="49"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
     </row>
@@ -6248,46 +6380,46 @@
       <c r="N5" s="13"/>
       <c r="O5" s="12"/>
       <c r="P5" s="13"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47" t="s">
+      <c r="Q5" s="54"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="T5" s="47"/>
+      <c r="T5" s="49"/>
       <c r="U5" s="15"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
-      <c r="X5" s="47"/>
+      <c r="X5" s="49"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
     </row>
     <row r="6" spans="1:26" ht="17.25">
       <c r="A6" s="8"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47" t="s">
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="49"/>
       <c r="U6" s="15"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
     </row>
     <row r="7" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A7" s="8" t="s">
@@ -6314,109 +6446,127 @@
       <c r="J7" s="13"/>
       <c r="K7" s="12"/>
       <c r="L7" s="13"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="13"/>
+      <c r="M7" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="N7" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="O7" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47" t="s">
+        <v>158</v>
+      </c>
+      <c r="P7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="T7" s="47"/>
+      <c r="T7" s="49"/>
       <c r="U7" s="15"/>
-      <c r="V7" s="47"/>
-      <c r="W7" s="47"/>
-      <c r="X7" s="47"/>
-      <c r="Y7" s="47"/>
-      <c r="Z7" s="47"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
     </row>
     <row r="8" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A8" s="8"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="12"/>
       <c r="J8" s="13"/>
       <c r="K8" s="12"/>
       <c r="L8" s="13"/>
-      <c r="M8" s="12"/>
+      <c r="M8" s="12" t="s">
+        <v>162</v>
+      </c>
       <c r="N8" s="13"/>
-      <c r="O8" s="12"/>
+      <c r="O8" s="12" t="s">
+        <v>163</v>
+      </c>
       <c r="P8" s="13"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47" t="s">
+      <c r="Q8" s="54"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="T8" s="47"/>
+      <c r="T8" s="49"/>
       <c r="U8" s="15"/>
-      <c r="V8" s="47"/>
+      <c r="V8" s="49"/>
       <c r="W8" s="7"/>
-      <c r="X8" s="47"/>
-      <c r="Y8" s="47"/>
-      <c r="Z8" s="47"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
+      <c r="Z8" s="49"/>
     </row>
     <row r="9" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A9" s="8"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>14</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="H9" s="13"/>
+        <v>166</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="I9" s="12"/>
       <c r="J9" s="13"/>
       <c r="K9" s="12"/>
       <c r="L9" s="13"/>
       <c r="M9" s="12"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
-      <c r="T9" s="47"/>
+      <c r="O9" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q9" s="54"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
       <c r="U9" s="15"/>
       <c r="V9" s="17"/>
       <c r="W9" s="18"/>
       <c r="X9" s="17"/>
-      <c r="Y9" s="47"/>
-      <c r="Z9" s="47"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
     </row>
     <row r="10" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A10" s="47"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12"/>
       <c r="D10" s="13"/>
       <c r="E10" s="12"/>
       <c r="F10" s="13"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="12" t="s">
+        <v>168</v>
+      </c>
       <c r="H10" s="13"/>
       <c r="I10" s="12"/>
       <c r="J10" s="13"/>
@@ -6424,29 +6574,31 @@
       <c r="L10" s="13"/>
       <c r="M10" s="12"/>
       <c r="N10" s="13"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
-      <c r="T10" s="47"/>
+      <c r="O10" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="54"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
       <c r="U10" s="15"/>
-      <c r="V10" s="47"/>
+      <c r="V10" s="49"/>
       <c r="W10" s="7"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="47"/>
-      <c r="Z10" s="47"/>
-    </row>
-    <row r="11" spans="1:26" s="36" customFormat="1" ht="17.25">
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
+    </row>
+    <row r="11" spans="1:26" s="36" customFormat="1" ht="34.5">
       <c r="A11" s="8"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12"/>
       <c r="D11" s="13"/>
       <c r="E11" s="12"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="12" t="s">
-        <v>164</v>
-      </c>
+      <c r="G11" s="12"/>
       <c r="H11" s="13"/>
       <c r="I11" s="12"/>
       <c r="J11" s="13"/>
@@ -6454,18 +6606,20 @@
       <c r="L11" s="13"/>
       <c r="M11" s="12"/>
       <c r="N11" s="13"/>
-      <c r="O11" s="47"/>
+      <c r="O11" s="14" t="s">
+        <v>170</v>
+      </c>
       <c r="P11" s="13"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
       <c r="U11" s="15"/>
-      <c r="V11" s="47"/>
-      <c r="W11" s="47"/>
-      <c r="X11" s="47"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="47"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
     </row>
     <row r="12" spans="1:26" s="36" customFormat="1" ht="17.25">
       <c r="A12" s="8"/>
@@ -6475,7 +6629,7 @@
       <c r="E12" s="14"/>
       <c r="F12" s="13"/>
       <c r="G12" s="12" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="12"/>
@@ -6484,18 +6638,22 @@
       <c r="L12" s="13"/>
       <c r="M12" s="12"/>
       <c r="N12" s="13"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
-      <c r="T12" s="47"/>
+      <c r="O12" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
       <c r="W12" s="17"/>
       <c r="X12" s="17"/>
-      <c r="Y12" s="47"/>
-      <c r="Z12" s="47"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
     </row>
     <row r="13" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A13" s="8"/>
@@ -6505,7 +6663,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="13"/>
       <c r="G13" s="12" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>14</v>
@@ -6518,28 +6676,28 @@
       <c r="N13" s="13"/>
       <c r="O13" s="12"/>
       <c r="P13" s="13"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="46" t="s">
+      <c r="Q13" s="54"/>
+      <c r="R13" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
     </row>
     <row r="14" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A14" s="47"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="11"/>
       <c r="C14" s="19"/>
       <c r="D14" s="13"/>
       <c r="E14" s="19"/>
       <c r="F14" s="13"/>
       <c r="G14" s="12" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>14</v>
@@ -6552,16 +6710,16 @@
       <c r="N14" s="13"/>
       <c r="O14" s="19"/>
       <c r="P14" s="13"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
+      <c r="Q14" s="54"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
     </row>
     <row r="15" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A15" s="8"/>
@@ -6571,9 +6729,11 @@
       <c r="E15" s="12"/>
       <c r="F15" s="13"/>
       <c r="G15" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="H15" s="13"/>
+        <v>175</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>14</v>
+      </c>
       <c r="I15" s="12"/>
       <c r="J15" s="13"/>
       <c r="K15" s="12"/>
@@ -6582,16 +6742,16 @@
       <c r="N15" s="13"/>
       <c r="O15" s="12"/>
       <c r="P15" s="13"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="47"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
     </row>
     <row r="16" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A16" s="8"/>
@@ -6601,7 +6761,7 @@
       <c r="E16" s="12"/>
       <c r="F16" s="13"/>
       <c r="G16" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="12"/>
@@ -6612,50 +6772,52 @@
       <c r="N16" s="13"/>
       <c r="O16" s="12"/>
       <c r="P16" s="13"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="47"/>
-      <c r="U16" s="47"/>
-      <c r="V16" s="47"/>
-      <c r="W16" s="47"/>
-      <c r="X16" s="47"/>
-      <c r="Y16" s="47"/>
-      <c r="Z16" s="47"/>
+      <c r="Q16" s="54"/>
+      <c r="R16" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
     </row>
     <row r="17" spans="1:20" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A17" s="8"/>
       <c r="B17" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="54"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="54"/>
-      <c r="L17" s="55"/>
-      <c r="M17" s="54"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="54"/>
-      <c r="P17" s="55"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="47"/>
-      <c r="T17" s="47"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="57"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="54"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
     </row>
     <row r="18" spans="1:20" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A18" s="47"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="11" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="13"/>
       <c r="E18" s="12" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>14</v>
@@ -6670,13 +6832,13 @@
       <c r="N18" s="13"/>
       <c r="O18" s="12"/>
       <c r="P18" s="13"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="47"/>
-      <c r="T18" s="47"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="49"/>
     </row>
     <row r="19" spans="1:20" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A19" s="47"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="11" t="s">
         <v>47</v>
       </c>
@@ -6698,53 +6860,53 @@
       <c r="N19" s="13"/>
       <c r="O19" s="12"/>
       <c r="P19" s="13"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="47"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
     </row>
     <row r="20" spans="1:20" s="36" customFormat="1" ht="17.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="47"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="47"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
       <c r="T20" s="10"/>
     </row>
     <row r="21" spans="1:20" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
-      <c r="N21" s="47"/>
-      <c r="O21" s="47"/>
-      <c r="P21" s="47"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
       <c r="Q21" s="7"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
       <c r="T21" s="10"/>
     </row>
     <row r="22" spans="1:20" s="36" customFormat="1" ht="30.75" customHeight="1">
@@ -6754,38 +6916,38 @@
       <c r="B22" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="58">
+      <c r="C22" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="62"/>
+      <c r="E22" s="61">
         <v>9</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="58">
-        <v>10</v>
-      </c>
-      <c r="H22" s="59"/>
-      <c r="I22" s="58">
+      <c r="F22" s="62"/>
+      <c r="G22" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="62"/>
+      <c r="I22" s="61">
         <v>11</v>
       </c>
-      <c r="J22" s="59"/>
-      <c r="K22" s="58">
+      <c r="J22" s="62"/>
+      <c r="K22" s="61">
         <v>12</v>
       </c>
-      <c r="L22" s="59"/>
-      <c r="M22" s="58">
+      <c r="L22" s="62"/>
+      <c r="M22" s="61">
         <v>13</v>
       </c>
-      <c r="N22" s="59"/>
-      <c r="O22" s="58">
-        <v>14</v>
-      </c>
-      <c r="P22" s="59"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="47"/>
-      <c r="T22" s="47"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="61">
+        <v>14</v>
+      </c>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="49"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="49"/>
     </row>
     <row r="23" spans="1:20" s="36" customFormat="1" ht="20.25">
       <c r="A23" s="22" t="s">
@@ -6794,26 +6956,26 @@
       <c r="B23" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="56"/>
-      <c r="L23" s="57"/>
-      <c r="M23" s="56"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="56"/>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
-      <c r="T23" s="47"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="59"/>
+      <c r="N23" s="60"/>
+      <c r="O23" s="59"/>
+      <c r="P23" s="60"/>
+      <c r="Q23" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="R23" s="49"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
     </row>
     <row r="24" spans="1:20" s="36" customFormat="1" ht="17.25">
       <c r="A24" s="8" t="s">
@@ -6836,32 +6998,34 @@
       <c r="N24" s="13"/>
       <c r="O24" s="14"/>
       <c r="P24" s="13"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="47"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="49"/>
       <c r="S24" s="23"/>
-      <c r="T24" s="47"/>
+      <c r="T24" s="49"/>
     </row>
     <row r="25" spans="1:20" s="36" customFormat="1" ht="28.5" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="47"/>
+      <c r="C25" s="49" t="s">
+        <v>153</v>
+      </c>
       <c r="D25" s="13"/>
       <c r="E25" s="14"/>
       <c r="F25" s="13"/>
-      <c r="G25" s="47"/>
+      <c r="G25" s="49"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
       <c r="J25" s="13"/>
       <c r="K25" s="14"/>
       <c r="L25" s="13"/>
-      <c r="M25" s="47"/>
+      <c r="M25" s="49"/>
       <c r="N25" s="13"/>
       <c r="O25" s="14"/>
       <c r="P25" s="13"/>
-      <c r="Q25" s="49"/>
-      <c r="R25" s="47"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="49"/>
       <c r="S25" s="25"/>
       <c r="T25" s="26"/>
     </row>
@@ -6884,7 +7048,7 @@
       <c r="N26" s="13"/>
       <c r="O26" s="12"/>
       <c r="P26" s="13"/>
-      <c r="Q26" s="49"/>
+      <c r="Q26" s="52"/>
       <c r="R26" s="27"/>
       <c r="S26" s="25"/>
       <c r="T26" s="26"/>
@@ -6892,21 +7056,21 @@
     <row r="27" spans="1:20" s="36" customFormat="1" ht="17.25">
       <c r="A27" s="8"/>
       <c r="B27" s="16"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-      <c r="E27" s="60"/>
-      <c r="F27" s="60"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-      <c r="I27" s="60"/>
-      <c r="J27" s="60"/>
-      <c r="K27" s="60"/>
-      <c r="L27" s="60"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="60"/>
-      <c r="O27" s="60"/>
-      <c r="P27" s="61"/>
-      <c r="Q27" s="49"/>
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" s="63"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="64"/>
+      <c r="Q27" s="52"/>
       <c r="R27" s="25"/>
       <c r="S27" s="25"/>
       <c r="T27" s="28"/>
@@ -6919,31 +7083,35 @@
         <v>25</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
       <c r="F28" s="13"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>182</v>
+      </c>
       <c r="H28" s="13"/>
       <c r="I28" s="12"/>
       <c r="J28" s="13"/>
-      <c r="K28" s="12"/>
+      <c r="K28" s="12" t="s">
+        <v>183</v>
+      </c>
       <c r="L28" s="13"/>
       <c r="M28" s="12"/>
       <c r="N28" s="13"/>
       <c r="O28" s="12"/>
       <c r="P28" s="13"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="47"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="49"/>
       <c r="S28" s="29"/>
-      <c r="T28" s="47"/>
+      <c r="T28" s="49"/>
     </row>
     <row r="29" spans="1:20" s="36" customFormat="1" ht="34.15" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="12"/>
@@ -6958,7 +7126,7 @@
       <c r="N29" s="13"/>
       <c r="O29" s="12"/>
       <c r="P29" s="13"/>
-      <c r="Q29" s="49"/>
+      <c r="Q29" s="52"/>
       <c r="R29" s="28"/>
       <c r="S29" s="23"/>
       <c r="T29" s="28"/>
@@ -6980,13 +7148,13 @@
       <c r="N30" s="13"/>
       <c r="O30" s="12"/>
       <c r="P30" s="13"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="47"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="49"/>
       <c r="S30" s="25"/>
       <c r="T30" s="28"/>
     </row>
     <row r="31" spans="1:20" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A31" s="47"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12"/>
       <c r="D31" s="13"/>
@@ -7002,7 +7170,7 @@
       <c r="N31" s="13"/>
       <c r="O31" s="12"/>
       <c r="P31" s="13"/>
-      <c r="Q31" s="49"/>
+      <c r="Q31" s="52"/>
       <c r="R31" s="28"/>
       <c r="S31" s="28"/>
       <c r="T31" s="28"/>
@@ -7024,7 +7192,7 @@
       <c r="N32" s="13"/>
       <c r="O32" s="12"/>
       <c r="P32" s="13"/>
-      <c r="Q32" s="49"/>
+      <c r="Q32" s="52"/>
       <c r="R32" s="30"/>
       <c r="S32" s="30"/>
       <c r="T32" s="30"/>
@@ -7046,16 +7214,16 @@
       <c r="N33" s="13"/>
       <c r="O33" s="12"/>
       <c r="P33" s="13"/>
-      <c r="Q33" s="49"/>
+      <c r="Q33" s="52"/>
       <c r="R33" s="30"/>
       <c r="S33" s="30"/>
       <c r="T33" s="30"/>
-      <c r="U33" s="47"/>
-      <c r="V33" s="47"/>
-      <c r="W33" s="47"/>
-      <c r="X33" s="47"/>
-      <c r="Y33" s="47"/>
-      <c r="Z33" s="47"/>
+      <c r="U33" s="49"/>
+      <c r="V33" s="49"/>
+      <c r="W33" s="49"/>
+      <c r="X33" s="49"/>
+      <c r="Y33" s="49"/>
+      <c r="Z33" s="49"/>
     </row>
     <row r="34" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A34" s="8"/>
@@ -7074,19 +7242,19 @@
       <c r="N34" s="13"/>
       <c r="O34" s="12"/>
       <c r="P34" s="13"/>
-      <c r="Q34" s="49"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="47"/>
-      <c r="T34" s="47"/>
-      <c r="U34" s="47"/>
-      <c r="V34" s="47"/>
-      <c r="W34" s="47"/>
-      <c r="X34" s="47"/>
-      <c r="Y34" s="47"/>
-      <c r="Z34" s="47"/>
+      <c r="Q34" s="52"/>
+      <c r="R34" s="49"/>
+      <c r="S34" s="49"/>
+      <c r="T34" s="49"/>
+      <c r="U34" s="49"/>
+      <c r="V34" s="49"/>
+      <c r="W34" s="49"/>
+      <c r="X34" s="49"/>
+      <c r="Y34" s="49"/>
+      <c r="Z34" s="49"/>
     </row>
     <row r="35" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A35" s="47"/>
+      <c r="A35" s="49"/>
       <c r="B35" s="11"/>
       <c r="C35" s="19"/>
       <c r="D35" s="13"/>
@@ -7102,16 +7270,16 @@
       <c r="N35" s="13"/>
       <c r="O35" s="19"/>
       <c r="P35" s="13"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="47"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="49"/>
       <c r="S35" s="31"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="47"/>
-      <c r="V35" s="47"/>
-      <c r="W35" s="47"/>
-      <c r="X35" s="47"/>
-      <c r="Y35" s="47"/>
-      <c r="Z35" s="47"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="49"/>
+      <c r="V35" s="49"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="49"/>
+      <c r="Y35" s="49"/>
+      <c r="Z35" s="49"/>
     </row>
     <row r="36" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
       <c r="A36" s="8"/>
@@ -7130,12 +7298,12 @@
       <c r="N36" s="13"/>
       <c r="O36" s="12"/>
       <c r="P36" s="13"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="47"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="49"/>
       <c r="S36" s="31"/>
-      <c r="T36" s="47"/>
-      <c r="U36" s="47"/>
-      <c r="V36" s="47"/>
+      <c r="T36" s="49"/>
+      <c r="U36" s="49"/>
+      <c r="V36" s="49"/>
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
       <c r="Y36" s="7"/>
@@ -7158,12 +7326,12 @@
       <c r="N37" s="13"/>
       <c r="O37" s="12"/>
       <c r="P37" s="13"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="47"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="49"/>
       <c r="S37" s="31"/>
-      <c r="T37" s="47"/>
-      <c r="U37" s="47"/>
-      <c r="V37" s="47"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="49"/>
       <c r="W37" s="7"/>
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
@@ -7174,33 +7342,33 @@
       <c r="B38" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="52"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="54"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="54"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="54"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="47"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="49"/>
       <c r="S38" s="31"/>
-      <c r="T38" s="47"/>
-      <c r="U38" s="47"/>
-      <c r="V38" s="47"/>
+      <c r="T38" s="49"/>
+      <c r="U38" s="49"/>
+      <c r="V38" s="49"/>
       <c r="W38" s="7"/>
       <c r="X38" s="7"/>
       <c r="Y38" s="7"/>
       <c r="Z38" s="7"/>
     </row>
     <row r="39" spans="1:26" s="36" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A39" s="47"/>
+      <c r="A39" s="49"/>
       <c r="B39" s="11" t="s">
         <v>46</v>
       </c>
@@ -7218,19 +7386,19 @@
       <c r="N39" s="13"/>
       <c r="O39" s="12"/>
       <c r="P39" s="13"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="47"/>
-      <c r="S39" s="47"/>
-      <c r="T39" s="47"/>
-      <c r="U39" s="47"/>
-      <c r="V39" s="47"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="49"/>
+      <c r="S39" s="49"/>
+      <c r="T39" s="49"/>
+      <c r="U39" s="49"/>
+      <c r="V39" s="49"/>
       <c r="W39" s="7"/>
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
     </row>
     <row r="40" spans="1:26" s="36" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A40" s="47"/>
+      <c r="A40" s="49"/>
       <c r="B40" s="11" t="s">
         <v>47</v>
       </c>
@@ -7248,68 +7416,68 @@
       <c r="N40" s="13"/>
       <c r="O40" s="12"/>
       <c r="P40" s="13"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="47"/>
-      <c r="S40" s="47"/>
-      <c r="T40" s="47"/>
-      <c r="U40" s="47"/>
-      <c r="V40" s="47"/>
-      <c r="W40" s="47"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="49"/>
+      <c r="S40" s="49"/>
+      <c r="T40" s="49"/>
+      <c r="U40" s="49"/>
+      <c r="V40" s="49"/>
+      <c r="W40" s="49"/>
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
     </row>
     <row r="41" spans="1:26" s="36" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A41" s="47"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="47"/>
-      <c r="I41" s="47"/>
-      <c r="J41" s="47"/>
-      <c r="K41" s="47"/>
-      <c r="L41" s="47"/>
-      <c r="M41" s="47"/>
-      <c r="N41" s="47"/>
-      <c r="O41" s="47"/>
-      <c r="P41" s="47"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
+      <c r="L41" s="49"/>
+      <c r="M41" s="49"/>
+      <c r="N41" s="49"/>
+      <c r="O41" s="49"/>
+      <c r="P41" s="49"/>
       <c r="Q41" s="7"/>
-      <c r="R41" s="47"/>
-      <c r="S41" s="47"/>
-      <c r="T41" s="47"/>
-      <c r="U41" s="47"/>
-      <c r="V41" s="47"/>
+      <c r="R41" s="49"/>
+      <c r="S41" s="49"/>
+      <c r="T41" s="49"/>
+      <c r="U41" s="49"/>
+      <c r="V41" s="49"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
     </row>
     <row r="42" spans="1:26" s="36" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A42" s="47"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="47"/>
-      <c r="K42" s="47"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
-      <c r="N42" s="47"/>
-      <c r="O42" s="47"/>
-      <c r="P42" s="47"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="J42" s="49"/>
+      <c r="K42" s="49"/>
+      <c r="L42" s="49"/>
+      <c r="M42" s="49"/>
+      <c r="N42" s="49"/>
+      <c r="O42" s="49"/>
+      <c r="P42" s="49"/>
       <c r="Q42" s="7"/>
-      <c r="R42" s="47"/>
+      <c r="R42" s="49"/>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
       <c r="U42" s="7"/>
-      <c r="V42" s="47"/>
+      <c r="V42" s="49"/>
       <c r="W42" s="7"/>
       <c r="X42" s="7"/>
       <c r="Y42" s="7"/>
@@ -7322,40 +7490,40 @@
       <c r="B43" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="58">
+      <c r="C43" s="61">
         <v>15</v>
       </c>
-      <c r="D43" s="59"/>
-      <c r="E43" s="58">
+      <c r="D43" s="62"/>
+      <c r="E43" s="61">
         <v>16</v>
       </c>
-      <c r="F43" s="59"/>
-      <c r="G43" s="58">
+      <c r="F43" s="62"/>
+      <c r="G43" s="61">
         <v>17</v>
       </c>
-      <c r="H43" s="59"/>
-      <c r="I43" s="58">
+      <c r="H43" s="62"/>
+      <c r="I43" s="61">
         <v>18</v>
       </c>
-      <c r="J43" s="59"/>
-      <c r="K43" s="58">
+      <c r="J43" s="62"/>
+      <c r="K43" s="61">
         <v>19</v>
       </c>
-      <c r="L43" s="59"/>
-      <c r="M43" s="58">
+      <c r="L43" s="62"/>
+      <c r="M43" s="61">
         <v>20</v>
       </c>
-      <c r="N43" s="59"/>
-      <c r="O43" s="58">
+      <c r="N43" s="62"/>
+      <c r="O43" s="61">
         <v>21</v>
       </c>
-      <c r="P43" s="59"/>
+      <c r="P43" s="62"/>
       <c r="Q43" s="7"/>
-      <c r="R43" s="47"/>
-      <c r="S43" s="47"/>
-      <c r="T43" s="47"/>
-      <c r="U43" s="47"/>
-      <c r="V43" s="47"/>
+      <c r="R43" s="49"/>
+      <c r="S43" s="49"/>
+      <c r="T43" s="49"/>
+      <c r="U43" s="49"/>
+      <c r="V43" s="49"/>
       <c r="W43" s="7"/>
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
@@ -7368,26 +7536,26 @@
       <c r="B44" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="57"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="57"/>
-      <c r="K44" s="56"/>
-      <c r="L44" s="57"/>
-      <c r="M44" s="56"/>
-      <c r="N44" s="57"/>
-      <c r="O44" s="56"/>
-      <c r="P44" s="57"/>
-      <c r="Q44" s="48"/>
-      <c r="R44" s="47"/>
-      <c r="S44" s="47"/>
-      <c r="T44" s="47"/>
-      <c r="U44" s="47"/>
-      <c r="V44" s="47"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="60"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="59"/>
+      <c r="P44" s="60"/>
+      <c r="Q44" s="51"/>
+      <c r="R44" s="49"/>
+      <c r="S44" s="49"/>
+      <c r="T44" s="49"/>
+      <c r="U44" s="49"/>
+      <c r="V44" s="49"/>
       <c r="W44" s="7"/>
       <c r="X44" s="7"/>
       <c r="Y44" s="7"/>
@@ -7414,12 +7582,12 @@
       <c r="N45" s="13"/>
       <c r="O45" s="14"/>
       <c r="P45" s="13"/>
-      <c r="Q45" s="49"/>
-      <c r="R45" s="47"/>
-      <c r="S45" s="47"/>
-      <c r="T45" s="47"/>
-      <c r="U45" s="47"/>
-      <c r="V45" s="47"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="49"/>
+      <c r="S45" s="49"/>
+      <c r="T45" s="49"/>
+      <c r="U45" s="49"/>
+      <c r="V45" s="49"/>
       <c r="W45" s="7"/>
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
@@ -7434,22 +7602,22 @@
       <c r="D46" s="13"/>
       <c r="E46" s="14"/>
       <c r="F46" s="13"/>
-      <c r="G46" s="47"/>
+      <c r="G46" s="49"/>
       <c r="H46" s="13"/>
       <c r="I46" s="14"/>
       <c r="J46" s="13"/>
-      <c r="K46" s="47"/>
+      <c r="K46" s="49"/>
       <c r="L46" s="13"/>
-      <c r="M46" s="47"/>
+      <c r="M46" s="49"/>
       <c r="N46" s="13"/>
       <c r="O46" s="14"/>
       <c r="P46" s="13"/>
-      <c r="Q46" s="49"/>
-      <c r="R46" s="47"/>
-      <c r="S46" s="47"/>
-      <c r="T46" s="47"/>
-      <c r="U46" s="47"/>
-      <c r="V46" s="47"/>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="49"/>
+      <c r="S46" s="49"/>
+      <c r="T46" s="49"/>
+      <c r="U46" s="49"/>
+      <c r="V46" s="49"/>
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
       <c r="Y46" s="7"/>
@@ -7474,12 +7642,12 @@
       <c r="N47" s="13"/>
       <c r="O47" s="12"/>
       <c r="P47" s="13"/>
-      <c r="Q47" s="49"/>
-      <c r="R47" s="47"/>
-      <c r="S47" s="47"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="49"/>
+      <c r="S47" s="49"/>
       <c r="T47" s="32"/>
-      <c r="U47" s="47"/>
-      <c r="V47" s="47"/>
+      <c r="U47" s="49"/>
+      <c r="V47" s="49"/>
       <c r="W47" s="7"/>
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
@@ -7488,26 +7656,26 @@
     <row r="48" spans="1:26" s="36" customFormat="1" ht="17.25">
       <c r="A48" s="8"/>
       <c r="B48" s="16"/>
-      <c r="C48" s="60"/>
-      <c r="D48" s="60"/>
-      <c r="E48" s="60"/>
-      <c r="F48" s="60"/>
-      <c r="G48" s="60"/>
-      <c r="H48" s="60"/>
-      <c r="I48" s="60"/>
-      <c r="J48" s="60"/>
-      <c r="K48" s="60"/>
-      <c r="L48" s="60"/>
-      <c r="M48" s="60"/>
-      <c r="N48" s="60"/>
-      <c r="O48" s="60"/>
-      <c r="P48" s="61"/>
-      <c r="Q48" s="49"/>
-      <c r="R48" s="47"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="63"/>
+      <c r="P48" s="64"/>
+      <c r="Q48" s="52"/>
+      <c r="R48" s="49"/>
       <c r="S48" s="10"/>
-      <c r="T48" s="47"/>
-      <c r="U48" s="47"/>
-      <c r="V48" s="47"/>
+      <c r="T48" s="49"/>
+      <c r="U48" s="49"/>
+      <c r="V48" s="49"/>
       <c r="W48" s="7"/>
       <c r="X48" s="7"/>
       <c r="Y48" s="7"/>
@@ -7534,14 +7702,14 @@
       <c r="N49" s="13"/>
       <c r="O49" s="12"/>
       <c r="P49" s="13"/>
-      <c r="Q49" s="49"/>
-      <c r="R49" s="46" t="s">
+      <c r="Q49" s="52"/>
+      <c r="R49" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="S49" s="47"/>
-      <c r="T49" s="47"/>
-      <c r="U49" s="47"/>
-      <c r="V49" s="47"/>
+      <c r="S49" s="49"/>
+      <c r="T49" s="49"/>
+      <c r="U49" s="49"/>
+      <c r="V49" s="49"/>
       <c r="W49" s="7"/>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
@@ -7564,14 +7732,14 @@
       <c r="N50" s="13"/>
       <c r="O50" s="12"/>
       <c r="P50" s="13"/>
-      <c r="Q50" s="49"/>
-      <c r="R50" s="47" t="s">
+      <c r="Q50" s="52"/>
+      <c r="R50" s="49" t="s">
         <v>94</v>
       </c>
       <c r="S50" s="31"/>
-      <c r="T50" s="47"/>
+      <c r="T50" s="49"/>
       <c r="U50" s="17"/>
-      <c r="V50" s="47"/>
+      <c r="V50" s="49"/>
       <c r="W50" s="7"/>
       <c r="X50" s="7"/>
       <c r="Y50" s="7"/>
@@ -7594,25 +7762,25 @@
       <c r="N51" s="13"/>
       <c r="O51" s="12"/>
       <c r="P51" s="13"/>
-      <c r="Q51" s="49"/>
-      <c r="R51" s="47" t="s">
+      <c r="Q51" s="52"/>
+      <c r="R51" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="S51" s="47" t="s">
+      <c r="S51" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="T51" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="U51" s="47"/>
-      <c r="V51" s="47"/>
+      <c r="T51" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="U51" s="49"/>
+      <c r="V51" s="49"/>
       <c r="W51" s="7"/>
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
     </row>
     <row r="52" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A52" s="47"/>
+      <c r="A52" s="49"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12"/>
       <c r="D52" s="13"/>
@@ -7628,18 +7796,18 @@
       <c r="N52" s="13"/>
       <c r="O52" s="12"/>
       <c r="P52" s="13"/>
-      <c r="Q52" s="49"/>
-      <c r="R52" s="47" t="s">
+      <c r="Q52" s="52"/>
+      <c r="R52" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="S52" s="47" t="s">
+      <c r="S52" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="T52" s="47" t="s">
-        <v>176</v>
-      </c>
-      <c r="U52" s="47"/>
-      <c r="V52" s="47"/>
+      <c r="T52" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="U52" s="49"/>
+      <c r="V52" s="49"/>
       <c r="W52" s="7"/>
       <c r="X52" s="7"/>
       <c r="Y52" s="7"/>
@@ -7662,18 +7830,18 @@
       <c r="N53" s="13"/>
       <c r="O53" s="12"/>
       <c r="P53" s="13"/>
-      <c r="Q53" s="49"/>
-      <c r="R53" s="47" t="s">
+      <c r="Q53" s="52"/>
+      <c r="R53" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="S53" s="47" t="s">
+      <c r="S53" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="T53" s="47" t="s">
-        <v>177</v>
+      <c r="T53" s="49" t="s">
+        <v>187</v>
       </c>
       <c r="U53" s="17"/>
-      <c r="V53" s="47"/>
+      <c r="V53" s="49"/>
       <c r="W53" s="7"/>
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
@@ -7696,18 +7864,18 @@
       <c r="N54" s="13"/>
       <c r="O54" s="12"/>
       <c r="P54" s="13"/>
-      <c r="Q54" s="49"/>
-      <c r="R54" s="47" t="s">
+      <c r="Q54" s="52"/>
+      <c r="R54" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="S54" s="47" t="s">
+      <c r="S54" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="T54" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="U54" s="47"/>
-      <c r="V54" s="47"/>
+      <c r="T54" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="U54" s="49"/>
+      <c r="V54" s="49"/>
       <c r="W54" s="7"/>
       <c r="X54" s="7"/>
       <c r="Y54" s="7"/>
@@ -7730,25 +7898,25 @@
       <c r="N55" s="13"/>
       <c r="O55" s="12"/>
       <c r="P55" s="13"/>
-      <c r="Q55" s="49"/>
-      <c r="R55" s="47" t="s">
+      <c r="Q55" s="52"/>
+      <c r="R55" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="S55" s="47" t="s">
+      <c r="S55" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="T55" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="U55" s="47"/>
-      <c r="V55" s="47"/>
+      <c r="T55" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="U55" s="49"/>
+      <c r="V55" s="49"/>
       <c r="W55" s="7"/>
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
     </row>
     <row r="56" spans="1:26" s="36" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A56" s="47"/>
+      <c r="A56" s="49"/>
       <c r="B56" s="11"/>
       <c r="C56" s="19"/>
       <c r="D56" s="13"/>
@@ -7764,16 +7932,16 @@
       <c r="N56" s="13"/>
       <c r="O56" s="19"/>
       <c r="P56" s="13"/>
-      <c r="Q56" s="49"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47" t="s">
+      <c r="Q56" s="52"/>
+      <c r="R56" s="49"/>
+      <c r="S56" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="T56" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="U56" s="47"/>
-      <c r="V56" s="47"/>
+      <c r="T56" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="U56" s="49"/>
+      <c r="V56" s="49"/>
       <c r="W56" s="7"/>
       <c r="X56" s="7"/>
       <c r="Y56" s="7"/>
@@ -7796,14 +7964,14 @@
       <c r="N57" s="13"/>
       <c r="O57" s="12"/>
       <c r="P57" s="13"/>
-      <c r="Q57" s="49"/>
-      <c r="R57" s="47"/>
-      <c r="S57" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="T57" s="47"/>
-      <c r="U57" s="47"/>
-      <c r="V57" s="47"/>
+      <c r="Q57" s="52"/>
+      <c r="R57" s="49"/>
+      <c r="S57" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="T57" s="49"/>
+      <c r="U57" s="49"/>
+      <c r="V57" s="49"/>
       <c r="W57" s="7"/>
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
@@ -7826,45 +7994,45 @@
       <c r="N58" s="13"/>
       <c r="O58" s="12"/>
       <c r="P58" s="13"/>
-      <c r="Q58" s="49"/>
-      <c r="R58" s="47"/>
-      <c r="S58" s="47" t="s">
+      <c r="Q58" s="52"/>
+      <c r="R58" s="49"/>
+      <c r="S58" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="T58" s="47"/>
-      <c r="U58" s="47"/>
-      <c r="V58" s="47"/>
+      <c r="T58" s="49"/>
+      <c r="U58" s="49"/>
+      <c r="V58" s="49"/>
     </row>
     <row r="59" spans="1:26" ht="30.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="52"/>
-      <c r="D59" s="53"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="53"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="55"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="54"/>
-      <c r="L59" s="55"/>
-      <c r="M59" s="54"/>
-      <c r="N59" s="55"/>
-      <c r="O59" s="54"/>
-      <c r="P59" s="55"/>
-      <c r="Q59" s="49"/>
-      <c r="R59" s="47"/>
-      <c r="S59" s="47" t="s">
+      <c r="C59" s="55"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="56"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="58"/>
+      <c r="K59" s="57"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="57"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="57"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="52"/>
+      <c r="R59" s="49"/>
+      <c r="S59" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="T59" s="47"/>
-      <c r="U59" s="47"/>
-      <c r="V59" s="47"/>
+      <c r="T59" s="49"/>
+      <c r="U59" s="49"/>
+      <c r="V59" s="49"/>
     </row>
     <row r="60" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A60" s="47"/>
+      <c r="A60" s="49"/>
       <c r="B60" s="11" t="s">
         <v>46</v>
       </c>
@@ -7882,17 +8050,17 @@
       <c r="N60" s="13"/>
       <c r="O60" s="12"/>
       <c r="P60" s="13"/>
-      <c r="Q60" s="49"/>
-      <c r="R60" s="47"/>
-      <c r="S60" s="47" t="s">
+      <c r="Q60" s="52"/>
+      <c r="R60" s="49"/>
+      <c r="S60" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="T60" s="47"/>
-      <c r="U60" s="47"/>
-      <c r="V60" s="47"/>
+      <c r="T60" s="49"/>
+      <c r="U60" s="49"/>
+      <c r="V60" s="49"/>
     </row>
     <row r="61" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A61" s="47"/>
+      <c r="A61" s="49"/>
       <c r="B61" s="11" t="s">
         <v>47</v>
       </c>
@@ -7910,8 +8078,8 @@
       <c r="N61" s="13"/>
       <c r="O61" s="12"/>
       <c r="P61" s="13"/>
-      <c r="Q61" s="49"/>
-      <c r="R61" s="47"/>
+      <c r="Q61" s="52"/>
+      <c r="R61" s="49"/>
       <c r="S61" s="33" t="s">
         <v>115</v>
       </c>
@@ -7920,50 +8088,50 @@
       <c r="V61" s="7"/>
     </row>
     <row r="62" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A62" s="47"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="47"/>
-      <c r="D62" s="47"/>
-      <c r="E62" s="47"/>
-      <c r="F62" s="47"/>
-      <c r="G62" s="47"/>
-      <c r="H62" s="47"/>
-      <c r="I62" s="47"/>
-      <c r="J62" s="47"/>
-      <c r="K62" s="47"/>
-      <c r="L62" s="47"/>
-      <c r="M62" s="47"/>
-      <c r="N62" s="47"/>
-      <c r="O62" s="47"/>
-      <c r="P62" s="47"/>
-      <c r="Q62" s="47"/>
-      <c r="R62" s="47"/>
-      <c r="S62" s="47"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="49"/>
+      <c r="M62" s="49"/>
+      <c r="N62" s="49"/>
+      <c r="O62" s="49"/>
+      <c r="P62" s="49"/>
+      <c r="Q62" s="49"/>
+      <c r="R62" s="49"/>
+      <c r="S62" s="49"/>
       <c r="T62" s="7"/>
       <c r="U62" s="7"/>
       <c r="V62" s="7"/>
     </row>
     <row r="63" spans="1:26" ht="30.75" customHeight="1">
-      <c r="A63" s="47"/>
-      <c r="B63" s="47"/>
-      <c r="C63" s="47"/>
-      <c r="D63" s="47"/>
-      <c r="E63" s="47"/>
-      <c r="F63" s="47"/>
-      <c r="G63" s="47"/>
-      <c r="H63" s="47"/>
-      <c r="I63" s="47"/>
-      <c r="J63" s="47"/>
-      <c r="K63" s="47"/>
-      <c r="L63" s="47"/>
-      <c r="M63" s="47"/>
-      <c r="N63" s="47"/>
-      <c r="O63" s="47"/>
-      <c r="P63" s="47"/>
-      <c r="Q63" s="47"/>
-      <c r="R63" s="47"/>
-      <c r="S63" s="47"/>
-      <c r="T63" s="47"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="49"/>
+      <c r="N63" s="49"/>
+      <c r="O63" s="49"/>
+      <c r="P63" s="49"/>
+      <c r="Q63" s="49"/>
+      <c r="R63" s="49"/>
+      <c r="S63" s="49"/>
+      <c r="T63" s="49"/>
       <c r="U63" s="17"/>
       <c r="V63" s="7"/>
     </row>
@@ -7974,38 +8142,38 @@
       <c r="B64" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C64" s="58">
+      <c r="C64" s="61">
         <v>22</v>
       </c>
-      <c r="D64" s="59"/>
-      <c r="E64" s="58">
+      <c r="D64" s="62"/>
+      <c r="E64" s="61">
         <v>23</v>
       </c>
-      <c r="F64" s="59"/>
-      <c r="G64" s="58">
+      <c r="F64" s="62"/>
+      <c r="G64" s="61">
         <v>24</v>
       </c>
-      <c r="H64" s="59"/>
-      <c r="I64" s="58">
+      <c r="H64" s="62"/>
+      <c r="I64" s="61">
         <v>25</v>
       </c>
-      <c r="J64" s="59"/>
-      <c r="K64" s="58">
+      <c r="J64" s="62"/>
+      <c r="K64" s="61">
         <v>26</v>
       </c>
-      <c r="L64" s="59"/>
-      <c r="M64" s="58">
+      <c r="L64" s="62"/>
+      <c r="M64" s="61">
         <v>27</v>
       </c>
-      <c r="N64" s="59"/>
-      <c r="O64" s="58">
+      <c r="N64" s="62"/>
+      <c r="O64" s="61">
         <v>28</v>
       </c>
-      <c r="P64" s="59"/>
-      <c r="Q64" s="47"/>
-      <c r="R64" s="47"/>
+      <c r="P64" s="62"/>
+      <c r="Q64" s="49"/>
+      <c r="R64" s="49"/>
       <c r="S64" s="34"/>
-      <c r="T64" s="47"/>
+      <c r="T64" s="49"/>
       <c r="U64" s="17"/>
       <c r="V64" s="7"/>
     </row>
@@ -8016,24 +8184,24 @@
       <c r="B65" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="56"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="56"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="56"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="56"/>
-      <c r="L65" s="57"/>
-      <c r="M65" s="56"/>
-      <c r="N65" s="57"/>
-      <c r="O65" s="56"/>
-      <c r="P65" s="57"/>
-      <c r="Q65" s="47"/>
-      <c r="R65" s="47"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="59"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="59"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="59"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="59"/>
+      <c r="P65" s="60"/>
+      <c r="Q65" s="49"/>
+      <c r="R65" s="49"/>
       <c r="S65" s="34"/>
-      <c r="T65" s="47"/>
+      <c r="T65" s="49"/>
       <c r="U65" s="17"/>
       <c r="V65" s="7"/>
     </row>
@@ -8058,10 +8226,10 @@
       <c r="N66" s="13"/>
       <c r="O66" s="14"/>
       <c r="P66" s="13"/>
-      <c r="Q66" s="47"/>
-      <c r="R66" s="47"/>
+      <c r="Q66" s="49"/>
+      <c r="R66" s="49"/>
       <c r="S66" s="34"/>
-      <c r="T66" s="47"/>
+      <c r="T66" s="49"/>
       <c r="U66" s="17"/>
       <c r="V66" s="7"/>
     </row>
@@ -8070,11 +8238,11 @@
       <c r="B67" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="47"/>
+      <c r="C67" s="49"/>
       <c r="D67" s="13"/>
       <c r="E67" s="14"/>
       <c r="F67" s="13"/>
-      <c r="G67" s="47"/>
+      <c r="G67" s="49"/>
       <c r="H67" s="13"/>
       <c r="I67" s="14"/>
       <c r="J67" s="13"/>
@@ -8084,8 +8252,8 @@
       <c r="N67" s="13"/>
       <c r="O67" s="14"/>
       <c r="P67" s="13"/>
-      <c r="Q67" s="47"/>
-      <c r="R67" s="47"/>
+      <c r="Q67" s="49"/>
+      <c r="R67" s="49"/>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
@@ -8110,8 +8278,8 @@
       <c r="N68" s="13"/>
       <c r="O68" s="12"/>
       <c r="P68" s="13"/>
-      <c r="Q68" s="47"/>
-      <c r="R68" s="47"/>
+      <c r="Q68" s="49"/>
+      <c r="R68" s="49"/>
       <c r="S68" s="7"/>
       <c r="T68" s="7"/>
       <c r="U68" s="7"/>
@@ -8122,22 +8290,22 @@
       <c r="B69" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="60"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="60"/>
-      <c r="F69" s="60"/>
-      <c r="G69" s="60"/>
-      <c r="H69" s="60"/>
-      <c r="I69" s="60"/>
-      <c r="J69" s="60"/>
-      <c r="K69" s="60"/>
-      <c r="L69" s="60"/>
-      <c r="M69" s="60"/>
-      <c r="N69" s="60"/>
-      <c r="O69" s="60"/>
-      <c r="P69" s="61"/>
-      <c r="Q69" s="47"/>
-      <c r="R69" s="47"/>
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="63"/>
+      <c r="F69" s="63"/>
+      <c r="G69" s="63"/>
+      <c r="H69" s="63"/>
+      <c r="I69" s="63"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="63"/>
+      <c r="L69" s="63"/>
+      <c r="M69" s="63"/>
+      <c r="N69" s="63"/>
+      <c r="O69" s="63"/>
+      <c r="P69" s="64"/>
+      <c r="Q69" s="49"/>
+      <c r="R69" s="49"/>
       <c r="S69" s="7"/>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
@@ -8164,9 +8332,9 @@
       <c r="N70" s="13"/>
       <c r="O70" s="12"/>
       <c r="P70" s="13"/>
-      <c r="Q70" s="47"/>
-      <c r="R70" s="47"/>
-      <c r="S70" s="47"/>
+      <c r="Q70" s="49"/>
+      <c r="R70" s="49"/>
+      <c r="S70" s="49"/>
       <c r="T70" s="7"/>
       <c r="U70" s="7"/>
       <c r="V70" s="7"/>
@@ -8188,8 +8356,8 @@
       <c r="N71" s="13"/>
       <c r="O71" s="12"/>
       <c r="P71" s="13"/>
-      <c r="R71" s="47"/>
-      <c r="S71" s="47"/>
+      <c r="R71" s="49"/>
+      <c r="S71" s="49"/>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
@@ -8211,14 +8379,14 @@
       <c r="N72" s="13"/>
       <c r="O72" s="12"/>
       <c r="P72" s="13"/>
-      <c r="R72" s="47"/>
-      <c r="S72" s="47"/>
+      <c r="R72" s="49"/>
+      <c r="S72" s="49"/>
       <c r="T72" s="7"/>
       <c r="U72" s="7"/>
       <c r="V72" s="7"/>
     </row>
     <row r="73" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A73" s="47"/>
+      <c r="A73" s="49"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12"/>
       <c r="D73" s="13"/>
@@ -8234,8 +8402,8 @@
       <c r="N73" s="13"/>
       <c r="O73" s="12"/>
       <c r="P73" s="13"/>
-      <c r="R73" s="47"/>
-      <c r="S73" s="47"/>
+      <c r="R73" s="49"/>
+      <c r="S73" s="49"/>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -8257,8 +8425,8 @@
       <c r="N74" s="13"/>
       <c r="O74" s="12"/>
       <c r="P74" s="13"/>
-      <c r="R74" s="47"/>
-      <c r="S74" s="47"/>
+      <c r="R74" s="49"/>
+      <c r="S74" s="49"/>
       <c r="T74" s="7"/>
       <c r="U74" s="35"/>
       <c r="V74" s="7"/>
@@ -8280,8 +8448,8 @@
       <c r="N75" s="13"/>
       <c r="O75" s="12"/>
       <c r="P75" s="13"/>
-      <c r="R75" s="47"/>
-      <c r="S75" s="47"/>
+      <c r="R75" s="49"/>
+      <c r="S75" s="49"/>
       <c r="T75" s="7"/>
       <c r="U75" s="7"/>
       <c r="V75" s="7"/>
@@ -8303,14 +8471,14 @@
       <c r="N76" s="13"/>
       <c r="O76" s="12"/>
       <c r="P76" s="13"/>
-      <c r="R76" s="47"/>
-      <c r="S76" s="47"/>
+      <c r="R76" s="49"/>
+      <c r="S76" s="49"/>
       <c r="T76" s="7"/>
       <c r="U76" s="7"/>
       <c r="V76" s="7"/>
     </row>
     <row r="77" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A77" s="47"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="11"/>
       <c r="C77" s="19"/>
       <c r="D77" s="13"/>
@@ -8349,7 +8517,7 @@
       <c r="N78" s="13"/>
       <c r="O78" s="12"/>
       <c r="P78" s="13"/>
-      <c r="Q78" s="47"/>
+      <c r="Q78" s="49"/>
       <c r="R78" s="7"/>
       <c r="S78" s="7"/>
       <c r="T78" s="7"/>
@@ -8373,8 +8541,8 @@
       <c r="N79" s="13"/>
       <c r="O79" s="12"/>
       <c r="P79" s="13"/>
-      <c r="Q79" s="47"/>
-      <c r="R79" s="47"/>
+      <c r="Q79" s="49"/>
+      <c r="R79" s="49"/>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
       <c r="U79" s="7"/>
@@ -8385,29 +8553,29 @@
       <c r="B80" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="52"/>
-      <c r="D80" s="53"/>
-      <c r="E80" s="52"/>
-      <c r="F80" s="53"/>
-      <c r="G80" s="54"/>
-      <c r="H80" s="55"/>
-      <c r="I80" s="54"/>
-      <c r="J80" s="55"/>
-      <c r="K80" s="54"/>
-      <c r="L80" s="55"/>
-      <c r="M80" s="54"/>
-      <c r="N80" s="55"/>
-      <c r="O80" s="54"/>
-      <c r="P80" s="55"/>
-      <c r="Q80" s="47"/>
-      <c r="R80" s="47"/>
-      <c r="S80" s="47"/>
-      <c r="T80" s="47"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="56"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="56"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="58"/>
+      <c r="I80" s="57"/>
+      <c r="J80" s="58"/>
+      <c r="K80" s="57"/>
+      <c r="L80" s="58"/>
+      <c r="M80" s="57"/>
+      <c r="N80" s="58"/>
+      <c r="O80" s="57"/>
+      <c r="P80" s="58"/>
+      <c r="Q80" s="49"/>
+      <c r="R80" s="49"/>
+      <c r="S80" s="49"/>
+      <c r="T80" s="49"/>
       <c r="U80" s="7"/>
       <c r="V80" s="7"/>
     </row>
     <row r="81" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A81" s="47"/>
+      <c r="A81" s="49"/>
       <c r="B81" s="11" t="s">
         <v>46</v>
       </c>
@@ -8425,15 +8593,15 @@
       <c r="N81" s="13"/>
       <c r="O81" s="12"/>
       <c r="P81" s="13"/>
-      <c r="Q81" s="47"/>
-      <c r="R81" s="47"/>
-      <c r="S81" s="47"/>
-      <c r="T81" s="47"/>
+      <c r="Q81" s="49"/>
+      <c r="R81" s="49"/>
+      <c r="S81" s="49"/>
+      <c r="T81" s="49"/>
       <c r="U81" s="7"/>
       <c r="V81" s="7"/>
     </row>
     <row r="82" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A82" s="47"/>
+      <c r="A82" s="49"/>
       <c r="B82" s="11" t="s">
         <v>47</v>
       </c>
@@ -8451,49 +8619,49 @@
       <c r="N82" s="13"/>
       <c r="O82" s="12"/>
       <c r="P82" s="13"/>
-      <c r="Q82" s="47"/>
-      <c r="R82" s="47"/>
-      <c r="S82" s="47"/>
-      <c r="T82" s="47"/>
+      <c r="Q82" s="49"/>
+      <c r="R82" s="49"/>
+      <c r="S82" s="49"/>
+      <c r="T82" s="49"/>
       <c r="U82" s="7"/>
       <c r="V82" s="7"/>
     </row>
     <row r="83" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A83" s="47"/>
-      <c r="B83" s="47"/>
-      <c r="C83" s="47"/>
-      <c r="D83" s="47"/>
-      <c r="E83" s="47"/>
-      <c r="F83" s="47"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="47"/>
-      <c r="I83" s="47"/>
-      <c r="J83" s="47"/>
-      <c r="K83" s="47"/>
-      <c r="L83" s="47"/>
-      <c r="M83" s="47"/>
-      <c r="N83" s="47"/>
-      <c r="O83" s="47"/>
-      <c r="P83" s="47"/>
-      <c r="Q83" s="47"/>
-      <c r="R83" s="47"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="49"/>
+      <c r="E83" s="49"/>
+      <c r="F83" s="49"/>
+      <c r="G83" s="49"/>
+      <c r="H83" s="49"/>
+      <c r="I83" s="49"/>
+      <c r="J83" s="49"/>
+      <c r="K83" s="49"/>
+      <c r="L83" s="49"/>
+      <c r="M83" s="49"/>
+      <c r="N83" s="49"/>
+      <c r="O83" s="49"/>
+      <c r="P83" s="49"/>
+      <c r="Q83" s="49"/>
+      <c r="R83" s="49"/>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
       <c r="U83" s="7"/>
       <c r="V83" s="7"/>
     </row>
     <row r="84" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A84" s="47"/>
-      <c r="B84" s="47"/>
-      <c r="C84" s="47"/>
-      <c r="D84" s="47"/>
-      <c r="E84" s="47"/>
-      <c r="F84" s="47"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="47"/>
-      <c r="I84" s="47"/>
-      <c r="J84" s="47"/>
-      <c r="K84" s="47"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="49"/>
+      <c r="E84" s="49"/>
+      <c r="F84" s="49"/>
+      <c r="G84" s="49"/>
+      <c r="H84" s="49"/>
+      <c r="I84" s="49"/>
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
       <c r="L84" s="7"/>
       <c r="M84" s="7"/>
       <c r="N84" s="7"/>
@@ -8512,21 +8680,21 @@
       <c r="B85" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="58">
+      <c r="C85" s="61">
         <v>29</v>
       </c>
-      <c r="D85" s="59"/>
-      <c r="E85" s="58">
+      <c r="D85" s="62"/>
+      <c r="E85" s="61">
         <v>30</v>
       </c>
-      <c r="F85" s="59"/>
-      <c r="G85" s="58">
+      <c r="F85" s="62"/>
+      <c r="G85" s="61">
         <v>31</v>
       </c>
-      <c r="H85" s="59"/>
-      <c r="I85" s="47"/>
-      <c r="J85" s="47"/>
-      <c r="K85" s="47"/>
+      <c r="H85" s="62"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+      <c r="K85" s="49"/>
       <c r="L85" s="7"/>
       <c r="M85" s="7"/>
       <c r="N85" s="7"/>
@@ -8545,15 +8713,15 @@
       <c r="B86" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C86" s="56"/>
-      <c r="D86" s="57"/>
-      <c r="E86" s="56"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="56"/>
-      <c r="H86" s="57"/>
-      <c r="I86" s="47"/>
-      <c r="J86" s="47"/>
-      <c r="K86" s="47"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="60"/>
+      <c r="I86" s="49"/>
+      <c r="J86" s="49"/>
+      <c r="K86" s="49"/>
       <c r="L86" s="7"/>
       <c r="M86" s="7"/>
       <c r="N86" s="7"/>
@@ -8578,9 +8746,9 @@
       <c r="F87" s="13"/>
       <c r="G87" s="14"/>
       <c r="H87" s="13"/>
-      <c r="I87" s="47"/>
-      <c r="J87" s="47"/>
-      <c r="K87" s="47"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="49"/>
+      <c r="K87" s="49"/>
       <c r="L87" s="7"/>
       <c r="M87" s="7"/>
       <c r="N87" s="7"/>
@@ -8601,11 +8769,11 @@
       <c r="D88" s="13"/>
       <c r="E88" s="14"/>
       <c r="F88" s="13"/>
-      <c r="G88" s="47"/>
+      <c r="G88" s="49"/>
       <c r="H88" s="13"/>
-      <c r="I88" s="47"/>
-      <c r="J88" s="47"/>
-      <c r="K88" s="47"/>
+      <c r="I88" s="49"/>
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
       <c r="L88" s="7"/>
       <c r="M88" s="7"/>
       <c r="N88" s="7"/>
@@ -8628,9 +8796,9 @@
       <c r="F89" s="13"/>
       <c r="G89" s="12"/>
       <c r="H89" s="13"/>
-      <c r="I89" s="47"/>
-      <c r="J89" s="47"/>
-      <c r="K89" s="47"/>
+      <c r="I89" s="49"/>
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
       <c r="L89" s="7"/>
       <c r="M89" s="7"/>
       <c r="N89" s="7"/>
@@ -8647,15 +8815,15 @@
       <c r="B90" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="60"/>
-      <c r="D90" s="60"/>
-      <c r="E90" s="60"/>
-      <c r="F90" s="60"/>
-      <c r="G90" s="54"/>
-      <c r="H90" s="55"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="47"/>
-      <c r="K90" s="47"/>
+      <c r="C90" s="63"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="58"/>
+      <c r="I90" s="49"/>
+      <c r="J90" s="49"/>
+      <c r="K90" s="49"/>
       <c r="L90" s="7"/>
       <c r="M90" s="7"/>
       <c r="N90" s="7"/>
@@ -8680,9 +8848,9 @@
       <c r="F91" s="13"/>
       <c r="G91" s="12"/>
       <c r="H91" s="13"/>
-      <c r="I91" s="47"/>
-      <c r="J91" s="47"/>
-      <c r="K91" s="47"/>
+      <c r="I91" s="49"/>
+      <c r="J91" s="49"/>
+      <c r="K91" s="49"/>
       <c r="L91" s="7"/>
       <c r="M91" s="7"/>
       <c r="N91" s="7"/>
@@ -8703,9 +8871,9 @@
       <c r="F92" s="13"/>
       <c r="G92" s="12"/>
       <c r="H92" s="13"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="47"/>
-      <c r="K92" s="47"/>
+      <c r="I92" s="49"/>
+      <c r="J92" s="49"/>
+      <c r="K92" s="49"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
       <c r="N92" s="7"/>
@@ -8726,9 +8894,9 @@
       <c r="F93" s="13"/>
       <c r="G93" s="12"/>
       <c r="H93" s="13"/>
-      <c r="I93" s="47"/>
-      <c r="J93" s="47"/>
-      <c r="K93" s="47"/>
+      <c r="I93" s="49"/>
+      <c r="J93" s="49"/>
+      <c r="K93" s="49"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
@@ -8741,7 +8909,7 @@
       <c r="V93" s="7"/>
     </row>
     <row r="94" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A94" s="47"/>
+      <c r="A94" s="49"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12"/>
       <c r="D94" s="13"/>
@@ -8749,9 +8917,9 @@
       <c r="F94" s="13"/>
       <c r="G94" s="12"/>
       <c r="H94" s="13"/>
-      <c r="I94" s="47"/>
-      <c r="J94" s="47"/>
-      <c r="K94" s="47"/>
+      <c r="I94" s="49"/>
+      <c r="J94" s="49"/>
+      <c r="K94" s="49"/>
       <c r="L94" s="7"/>
       <c r="M94" s="7"/>
       <c r="N94" s="7"/>
@@ -8772,9 +8940,9 @@
       <c r="F95" s="13"/>
       <c r="G95" s="12"/>
       <c r="H95" s="13"/>
-      <c r="I95" s="47"/>
-      <c r="J95" s="47"/>
-      <c r="K95" s="47"/>
+      <c r="I95" s="49"/>
+      <c r="J95" s="49"/>
+      <c r="K95" s="49"/>
       <c r="L95" s="7"/>
       <c r="M95" s="7"/>
       <c r="N95" s="7"/>
@@ -8795,9 +8963,9 @@
       <c r="F96" s="13"/>
       <c r="G96" s="12"/>
       <c r="H96" s="13"/>
-      <c r="I96" s="47"/>
-      <c r="J96" s="47"/>
-      <c r="K96" s="47"/>
+      <c r="I96" s="49"/>
+      <c r="J96" s="49"/>
+      <c r="K96" s="49"/>
       <c r="L96" s="7"/>
       <c r="M96" s="7"/>
       <c r="N96" s="7"/>
@@ -8818,9 +8986,9 @@
       <c r="F97" s="13"/>
       <c r="G97" s="12"/>
       <c r="H97" s="13"/>
-      <c r="I97" s="47"/>
-      <c r="J97" s="47"/>
-      <c r="K97" s="47"/>
+      <c r="I97" s="49"/>
+      <c r="J97" s="49"/>
+      <c r="K97" s="49"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
       <c r="N97" s="7"/>
@@ -8833,7 +9001,7 @@
       <c r="V97" s="7"/>
     </row>
     <row r="98" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A98" s="47"/>
+      <c r="A98" s="49"/>
       <c r="B98" s="11"/>
       <c r="C98" s="19"/>
       <c r="D98" s="13"/>
@@ -8841,9 +9009,9 @@
       <c r="F98" s="13"/>
       <c r="G98" s="12"/>
       <c r="H98" s="13"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="47"/>
-      <c r="K98" s="47"/>
+      <c r="I98" s="49"/>
+      <c r="J98" s="49"/>
+      <c r="K98" s="49"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
       <c r="N98" s="7"/>
@@ -8864,9 +9032,9 @@
       <c r="F99" s="13"/>
       <c r="G99" s="12"/>
       <c r="H99" s="13"/>
-      <c r="I99" s="47"/>
-      <c r="J99" s="47"/>
-      <c r="K99" s="47"/>
+      <c r="I99" s="49"/>
+      <c r="J99" s="49"/>
+      <c r="K99" s="49"/>
       <c r="L99" s="7"/>
       <c r="M99" s="7"/>
       <c r="N99" s="7"/>
@@ -8887,9 +9055,9 @@
       <c r="F100" s="13"/>
       <c r="G100" s="12"/>
       <c r="H100" s="13"/>
-      <c r="I100" s="47"/>
-      <c r="J100" s="47"/>
-      <c r="K100" s="47"/>
+      <c r="I100" s="49"/>
+      <c r="J100" s="49"/>
+      <c r="K100" s="49"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
       <c r="N100" s="7"/>
@@ -8906,15 +9074,15 @@
       <c r="B101" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C101" s="52"/>
-      <c r="D101" s="53"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="54"/>
-      <c r="H101" s="55"/>
-      <c r="I101" s="47"/>
-      <c r="J101" s="47"/>
-      <c r="K101" s="47"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="56"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="56"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="58"/>
+      <c r="I101" s="49"/>
+      <c r="J101" s="49"/>
+      <c r="K101" s="49"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
       <c r="N101" s="7"/>
@@ -8927,7 +9095,7 @@
       <c r="V101" s="7"/>
     </row>
     <row r="102" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A102" s="47"/>
+      <c r="A102" s="49"/>
       <c r="B102" s="11" t="s">
         <v>46</v>
       </c>
@@ -8937,9 +9105,9 @@
       <c r="F102" s="13"/>
       <c r="G102" s="12"/>
       <c r="H102" s="13"/>
-      <c r="I102" s="47"/>
-      <c r="J102" s="47"/>
-      <c r="K102" s="47"/>
+      <c r="I102" s="49"/>
+      <c r="J102" s="49"/>
+      <c r="K102" s="49"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
       <c r="N102" s="7"/>
@@ -8952,7 +9120,7 @@
       <c r="V102" s="7"/>
     </row>
     <row r="103" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A103" s="47"/>
+      <c r="A103" s="49"/>
       <c r="B103" s="11" t="s">
         <v>47</v>
       </c>
@@ -8962,9 +9130,9 @@
       <c r="F103" s="13"/>
       <c r="G103" s="12"/>
       <c r="H103" s="13"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="47"/>
-      <c r="K103" s="47"/>
+      <c r="I103" s="49"/>
+      <c r="J103" s="49"/>
+      <c r="K103" s="49"/>
       <c r="L103" s="7"/>
       <c r="M103" s="7"/>
       <c r="N103" s="7"/>
@@ -8977,17 +9145,17 @@
       <c r="V103" s="7"/>
     </row>
     <row r="104" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A104" s="47"/>
-      <c r="B104" s="47"/>
-      <c r="C104" s="47"/>
-      <c r="D104" s="47"/>
-      <c r="E104" s="47"/>
-      <c r="F104" s="47"/>
-      <c r="G104" s="47"/>
-      <c r="H104" s="47"/>
-      <c r="I104" s="47"/>
-      <c r="J104" s="47"/>
-      <c r="K104" s="47"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="49"/>
+      <c r="C104" s="49"/>
+      <c r="D104" s="49"/>
+      <c r="E104" s="49"/>
+      <c r="F104" s="49"/>
+      <c r="G104" s="49"/>
+      <c r="H104" s="49"/>
+      <c r="I104" s="49"/>
+      <c r="J104" s="49"/>
+      <c r="K104" s="49"/>
       <c r="L104" s="7"/>
       <c r="M104" s="7"/>
       <c r="N104" s="7"/>
@@ -9000,12 +9168,12 @@
       <c r="V104" s="7"/>
     </row>
     <row r="105" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A105" s="47"/>
-      <c r="B105" s="47"/>
-      <c r="C105" s="47"/>
-      <c r="D105" s="47"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="47"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="49"/>
+      <c r="C105" s="49"/>
+      <c r="D105" s="49"/>
+      <c r="E105" s="49"/>
+      <c r="F105" s="49"/>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
@@ -9023,12 +9191,12 @@
       <c r="V105" s="7"/>
     </row>
     <row r="106" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A106" s="47"/>
-      <c r="B106" s="47"/>
-      <c r="C106" s="47"/>
-      <c r="D106" s="47"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="47"/>
+      <c r="A106" s="49"/>
+      <c r="B106" s="49"/>
+      <c r="C106" s="49"/>
+      <c r="D106" s="49"/>
+      <c r="E106" s="49"/>
+      <c r="F106" s="49"/>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
@@ -9046,17 +9214,17 @@
       <c r="V106" s="7"/>
     </row>
     <row r="107" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A107" s="47"/>
-      <c r="B107" s="47"/>
-      <c r="C107" s="47"/>
-      <c r="D107" s="47"/>
-      <c r="E107" s="47"/>
-      <c r="F107" s="47"/>
-      <c r="G107" s="47"/>
-      <c r="H107" s="47"/>
-      <c r="I107" s="47"/>
-      <c r="J107" s="47"/>
-      <c r="K107" s="47"/>
+      <c r="A107" s="49"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="49"/>
+      <c r="D107" s="49"/>
+      <c r="E107" s="49"/>
+      <c r="F107" s="49"/>
+      <c r="G107" s="49"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="49"/>
+      <c r="J107" s="49"/>
+      <c r="K107" s="49"/>
       <c r="L107" s="7"/>
       <c r="M107" s="7"/>
       <c r="N107" s="7"/>
@@ -9069,17 +9237,17 @@
       <c r="V107" s="7"/>
     </row>
     <row r="108" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A108" s="47"/>
-      <c r="B108" s="47"/>
-      <c r="C108" s="47"/>
-      <c r="D108" s="47"/>
-      <c r="E108" s="47"/>
-      <c r="F108" s="47"/>
-      <c r="G108" s="47"/>
-      <c r="H108" s="47"/>
-      <c r="I108" s="47"/>
-      <c r="J108" s="47"/>
-      <c r="K108" s="47"/>
+      <c r="A108" s="49"/>
+      <c r="B108" s="49"/>
+      <c r="C108" s="49"/>
+      <c r="D108" s="49"/>
+      <c r="E108" s="49"/>
+      <c r="F108" s="49"/>
+      <c r="G108" s="49"/>
+      <c r="H108" s="49"/>
+      <c r="I108" s="49"/>
+      <c r="J108" s="49"/>
+      <c r="K108" s="49"/>
       <c r="L108" s="7"/>
       <c r="M108" s="7"/>
       <c r="N108" s="7"/>
@@ -9092,17 +9260,17 @@
       <c r="V108" s="7"/>
     </row>
     <row r="109" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A109" s="47"/>
-      <c r="B109" s="47"/>
-      <c r="C109" s="47"/>
-      <c r="D109" s="47"/>
-      <c r="E109" s="47"/>
-      <c r="F109" s="47"/>
-      <c r="G109" s="47"/>
-      <c r="H109" s="47"/>
-      <c r="I109" s="47"/>
-      <c r="J109" s="47"/>
-      <c r="K109" s="47"/>
+      <c r="A109" s="49"/>
+      <c r="B109" s="49"/>
+      <c r="C109" s="49"/>
+      <c r="D109" s="49"/>
+      <c r="E109" s="49"/>
+      <c r="F109" s="49"/>
+      <c r="G109" s="49"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="49"/>
+      <c r="J109" s="49"/>
+      <c r="K109" s="49"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
       <c r="N109" s="7"/>
@@ -9115,17 +9283,17 @@
       <c r="V109" s="7"/>
     </row>
     <row r="110" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A110" s="47"/>
-      <c r="B110" s="47"/>
-      <c r="C110" s="47"/>
-      <c r="D110" s="47"/>
-      <c r="E110" s="47"/>
-      <c r="F110" s="47"/>
-      <c r="G110" s="47"/>
-      <c r="H110" s="47"/>
-      <c r="I110" s="47"/>
-      <c r="J110" s="47"/>
-      <c r="K110" s="47"/>
+      <c r="A110" s="49"/>
+      <c r="B110" s="49"/>
+      <c r="C110" s="49"/>
+      <c r="D110" s="49"/>
+      <c r="E110" s="49"/>
+      <c r="F110" s="49"/>
+      <c r="G110" s="49"/>
+      <c r="H110" s="49"/>
+      <c r="I110" s="49"/>
+      <c r="J110" s="49"/>
+      <c r="K110" s="49"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
       <c r="N110" s="7"/>
@@ -9138,17 +9306,17 @@
       <c r="V110" s="7"/>
     </row>
     <row r="111" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A111" s="47"/>
-      <c r="B111" s="47"/>
-      <c r="C111" s="47"/>
-      <c r="D111" s="47"/>
-      <c r="E111" s="47"/>
-      <c r="F111" s="47"/>
-      <c r="G111" s="47"/>
-      <c r="H111" s="47"/>
-      <c r="I111" s="47"/>
-      <c r="J111" s="47"/>
-      <c r="K111" s="47"/>
+      <c r="A111" s="49"/>
+      <c r="B111" s="49"/>
+      <c r="C111" s="49"/>
+      <c r="D111" s="49"/>
+      <c r="E111" s="49"/>
+      <c r="F111" s="49"/>
+      <c r="G111" s="49"/>
+      <c r="H111" s="49"/>
+      <c r="I111" s="49"/>
+      <c r="J111" s="49"/>
+      <c r="K111" s="49"/>
       <c r="L111" s="7"/>
       <c r="M111" s="7"/>
       <c r="N111" s="7"/>
@@ -9161,17 +9329,17 @@
       <c r="V111" s="7"/>
     </row>
     <row r="112" spans="1:22" ht="30.75" customHeight="1">
-      <c r="A112" s="47"/>
-      <c r="B112" s="47"/>
-      <c r="C112" s="47"/>
-      <c r="D112" s="47"/>
-      <c r="E112" s="47"/>
-      <c r="F112" s="47"/>
-      <c r="G112" s="47"/>
-      <c r="H112" s="47"/>
-      <c r="I112" s="47"/>
-      <c r="J112" s="47"/>
-      <c r="K112" s="47"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="49"/>
+      <c r="C112" s="49"/>
+      <c r="D112" s="49"/>
+      <c r="E112" s="49"/>
+      <c r="F112" s="49"/>
+      <c r="G112" s="49"/>
+      <c r="H112" s="49"/>
+      <c r="I112" s="49"/>
+      <c r="J112" s="49"/>
+      <c r="K112" s="49"/>
       <c r="L112" s="7"/>
       <c r="M112" s="7"/>
       <c r="N112" s="7"/>
@@ -9496,15 +9664,16 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="R16" r:id="rId2" xr:uid="{C192EEA8-6F03-4447-94B2-53581D6B9918}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:J18"/>
+  <dimension ref="B1:J21"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="30"/>
@@ -9521,31 +9690,31 @@
   <sheetData>
     <row r="1" spans="2:10" s="17" customFormat="1" ht="21.75" customHeight="1">
       <c r="B1" s="41" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C1" s="41" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="H1" s="42" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="I1" s="42" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="J1" s="42" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="2:10">
@@ -9553,26 +9722,26 @@
         <v>45351</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="D2" s="44"/>
       <c r="E2" s="44">
         <v>264000</v>
       </c>
       <c r="F2" s="44" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G2" s="44" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="H2" s="45" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="I2" s="45" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="2:10" ht="49.5">
@@ -9580,23 +9749,23 @@
         <v>45420</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D3" s="44" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E3" s="44">
         <v>192500</v>
       </c>
       <c r="F3" s="44" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="H3" s="45"/>
       <c r="I3" s="45" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="J3" s="45"/>
     </row>
@@ -9605,26 +9774,26 @@
         <v>45482</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D4" s="44" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E4" s="44">
         <v>587000</v>
       </c>
       <c r="F4" s="44" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="H4" s="45"/>
       <c r="I4" s="45" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="33">
@@ -9632,24 +9801,24 @@
         <v>45513</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D5" s="44" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E5" s="44">
         <v>587000</v>
       </c>
       <c r="F5" s="44" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G5" s="44" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="H5" s="45"/>
       <c r="I5" s="45"/>
       <c r="J5" s="45" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -9657,15 +9826,15 @@
         <v>45518</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="44"/>
       <c r="F6" s="44" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G6" s="44" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="H6" s="45"/>
       <c r="I6" s="45"/>
@@ -9676,28 +9845,28 @@
         <v>45527</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E7" s="44">
         <v>264000</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G7" s="44" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="H7" s="45" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="I7" s="45" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="J7" s="45" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="33">
@@ -9705,26 +9874,26 @@
         <v>45555</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D8" s="44" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E8" s="44">
         <v>587000</v>
       </c>
       <c r="F8" s="44" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G8" s="44" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="H8" s="45"/>
       <c r="I8" s="45" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="J8" s="45" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="49.5">
@@ -9732,26 +9901,26 @@
         <v>45600</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E9" s="44">
         <v>42900</v>
       </c>
       <c r="F9" s="44" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="G9" s="44" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="H9" s="45"/>
       <c r="I9" s="45" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="J9" s="45" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="33">
@@ -9759,28 +9928,28 @@
         <v>45615</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E10" s="44">
         <v>160000</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G10" s="44" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H10" s="45" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="I10" s="45" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="2:10">
@@ -9788,16 +9957,16 @@
         <v>45621</v>
       </c>
       <c r="C11" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="44" t="s">
         <v>227</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>217</v>
       </c>
       <c r="E11" s="44">
         <v>2200</v>
       </c>
       <c r="F11" s="44" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G11" s="44"/>
       <c r="H11" s="45"/>
@@ -9809,25 +9978,25 @@
         <v>45621</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E12" s="44">
         <v>53900</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G12" s="44" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H12" s="45" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="I12" s="45" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="J12" s="45"/>
     </row>
@@ -9836,26 +10005,26 @@
         <v>45635</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="E13" s="44">
         <v>158400</v>
       </c>
       <c r="F13" s="44" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G13" s="44" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H13" s="45"/>
       <c r="I13" s="45" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="J13" s="45" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="33">
@@ -9863,28 +10032,28 @@
         <v>45660</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="E14" s="44">
         <v>38000</v>
       </c>
       <c r="F14" s="44" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G14" s="44" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H14" s="45" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="I14" s="45" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="J14" s="45" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="33">
@@ -9892,22 +10061,22 @@
         <v>45668</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E15" s="44">
         <v>135300</v>
       </c>
       <c r="F15" s="44" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G15" s="44" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="H15" s="45" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="I15" s="45"/>
       <c r="J15" s="45"/>
@@ -9917,20 +10086,20 @@
         <v>45687</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E16" s="44">
         <f>59000*1.1</f>
         <v>64900.000000000007</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H16" s="45"/>
       <c r="I16" s="45"/>
@@ -9941,15 +10110,15 @@
         <v>45696</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D17" s="44"/>
       <c r="E17" s="44"/>
       <c r="F17" s="44" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="H17" s="45"/>
       <c r="I17" s="45"/>
@@ -9958,22 +10127,65 @@
     <row r="18" spans="2:10">
       <c r="B18" s="44"/>
       <c r="C18" s="44" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E18" s="44">
         <v>40000</v>
       </c>
       <c r="F18" s="44" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="G18" s="44"/>
       <c r="H18" s="45"/>
       <c r="I18" s="45"/>
       <c r="J18" s="45" t="s">
-        <v>252</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="66">
+      <c r="B19" s="46">
+        <v>45694</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E19" s="15">
+        <v>53900</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="43">
+        <v>45696</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="E21" s="47">
+        <f>SUM(E2:E20)</f>
+        <v>3231000</v>
       </c>
     </row>
   </sheetData>
@@ -9984,12 +10196,13 @@
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="24.875" style="37" bestFit="1" customWidth="1"/>
@@ -10004,197 +10217,202 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="37" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="G1" s="37" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="66">
       <c r="A2" s="37" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="49.5">
       <c r="A3" s="37" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="82.5">
       <c r="A5" s="37" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="409.5">
       <c r="A6" s="37" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="66">
       <c r="A7" s="37" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="B7" s="38"/>
       <c r="F7" s="38" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="148.5">
       <c r="A8" s="37" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="E8" s="37" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="G8" s="37" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="148.5">
       <c r="A9" s="37" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="37" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="33">
       <c r="A11" s="37" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="82.5">
       <c r="A12" s="37" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="37" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="37" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="37" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="49.5">
       <c r="A16" s="37" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>274</v>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="37" t="s">
+        <v>319</v>
       </c>
     </row>
   </sheetData>
